--- a/data_inputs/daily_logs.xlsx
+++ b/data_inputs/daily_logs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://komaralliance-my.sharepoint.com/personal/dshao_komar_com/Documents/Production Logs/data_inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1239" documentId="8_{EA7A99F6-1694-487A-9FFB-F46B9189E3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D4E301C-0E97-4481-BD5F-FE25E87D239B}"/>
+  <xr:revisionPtr revIDLastSave="1704" documentId="8_{EA7A99F6-1694-487A-9FFB-F46B9189E3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9DA4253-FAE0-458D-9062-85927F44266E}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-12660" windowWidth="16440" windowHeight="28320" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="4" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6232" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7512" uniqueCount="90">
   <si>
     <t>Production Output</t>
   </si>
@@ -385,7 +385,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -419,6 +419,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -3327,7 +3328,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Shift/ Machine">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Shift/ Machine">
   <location ref="A21:E46" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending">
@@ -3513,7 +3514,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000001000000}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Machine">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000001000000}" name="PivotTable5" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Machine">
   <location ref="A5:E18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending">
@@ -4022,12 +4023,12 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
     </row>
     <row r="5" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
@@ -4278,12 +4279,12 @@
       <c r="E19" s="3"/>
     </row>
     <row r="20" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
     </row>
     <row r="21" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
@@ -7263,7 +7264,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G1372"/>
+  <dimension ref="A1:G1692"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
@@ -39316,7 +39317,7 @@
         <v>25</v>
       </c>
       <c r="D1372" s="24" t="str">
-        <f t="shared" ref="D1372" si="38">TEXT(B1372, "dddd")</f>
+        <f t="shared" ref="D1372:D1388" si="38">TEXT(B1372, "dddd")</f>
         <v>Friday</v>
       </c>
       <c r="E1372">
@@ -39326,6 +39327,7491 @@
         <v>40</v>
       </c>
       <c r="G1372" s="24" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1373" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1373" s="2">
+        <v>46055</v>
+      </c>
+      <c r="C1373" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1373" t="str">
+        <f t="shared" si="38"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1373">
+        <v>5220</v>
+      </c>
+      <c r="F1373" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1373" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1374" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1374" s="2">
+        <v>46055</v>
+      </c>
+      <c r="C1374" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1374" s="26" t="str">
+        <f t="shared" si="38"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1374">
+        <v>6004</v>
+      </c>
+      <c r="F1374" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1374" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1375" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1375" s="2">
+        <v>46055</v>
+      </c>
+      <c r="C1375" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1375" s="26" t="str">
+        <f t="shared" si="38"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1375">
+        <v>2468</v>
+      </c>
+      <c r="F1375" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1375" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1376" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1376" s="2">
+        <v>46055</v>
+      </c>
+      <c r="C1376" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1376" s="26" t="str">
+        <f t="shared" si="38"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1376">
+        <v>132</v>
+      </c>
+      <c r="F1376" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1376" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1377" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1377" s="2">
+        <v>46055</v>
+      </c>
+      <c r="C1377" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1377" s="26" t="str">
+        <f t="shared" si="38"/>
+        <v>Monday</v>
+      </c>
+      <c r="F1377" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1377" s="26" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1378" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1378" s="2">
+        <v>46055</v>
+      </c>
+      <c r="C1378" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1378" s="26" t="str">
+        <f t="shared" si="38"/>
+        <v>Monday</v>
+      </c>
+      <c r="F1378" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1378" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1379" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1379" s="2">
+        <v>46055</v>
+      </c>
+      <c r="C1379" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1379" s="26" t="str">
+        <f t="shared" si="38"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1379">
+        <v>3997</v>
+      </c>
+      <c r="F1379" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1379" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1380" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1380" s="2">
+        <v>46055</v>
+      </c>
+      <c r="C1380" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1380" s="26" t="str">
+        <f t="shared" si="38"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1380">
+        <v>5964</v>
+      </c>
+      <c r="F1380" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1380" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1381" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1381" s="2">
+        <v>46055</v>
+      </c>
+      <c r="C1381" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1381" s="26" t="str">
+        <f t="shared" si="38"/>
+        <v>Monday</v>
+      </c>
+      <c r="F1381" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1381" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1382" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1382" s="2">
+        <v>46055</v>
+      </c>
+      <c r="C1382" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1382" s="26" t="str">
+        <f t="shared" si="38"/>
+        <v>Monday</v>
+      </c>
+      <c r="F1382" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1382" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1383" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1383" s="2">
+        <v>46055</v>
+      </c>
+      <c r="C1383" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1383" s="26" t="str">
+        <f t="shared" si="38"/>
+        <v>Monday</v>
+      </c>
+      <c r="F1383" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1383" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1384" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1384" s="2">
+        <v>46055</v>
+      </c>
+      <c r="C1384" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1384" s="26" t="str">
+        <f t="shared" si="38"/>
+        <v>Monday</v>
+      </c>
+      <c r="F1384" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1384" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1385" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1385" s="2">
+        <v>46055</v>
+      </c>
+      <c r="C1385" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1385" s="26" t="str">
+        <f t="shared" si="38"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1385">
+        <v>2369</v>
+      </c>
+      <c r="F1385" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1385" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1386" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1386" s="2">
+        <v>46055</v>
+      </c>
+      <c r="C1386" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1386" s="26" t="str">
+        <f t="shared" si="38"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1386">
+        <v>8588</v>
+      </c>
+      <c r="F1386" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1386" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1387" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1387" s="2">
+        <v>46055</v>
+      </c>
+      <c r="C1387" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1387" s="26" t="str">
+        <f t="shared" si="38"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1387">
+        <v>2750</v>
+      </c>
+      <c r="F1387" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1387" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1388" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1388" s="2">
+        <v>46055</v>
+      </c>
+      <c r="C1388" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1388" s="26" t="str">
+        <f t="shared" si="38"/>
+        <v>Monday</v>
+      </c>
+      <c r="F1388" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1388" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1389" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1389" s="2">
+        <v>46056</v>
+      </c>
+      <c r="C1389" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1389" s="26" t="str">
+        <f t="shared" ref="D1389:D1404" si="39">TEXT(B1389, "dddd")</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1389">
+        <v>2489.6</v>
+      </c>
+      <c r="F1389" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1389" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1390" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1390" s="2">
+        <v>46056</v>
+      </c>
+      <c r="C1390" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1390" s="26" t="str">
+        <f t="shared" si="39"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1390">
+        <v>3286</v>
+      </c>
+      <c r="F1390" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1390" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1391" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1391" s="2">
+        <v>46056</v>
+      </c>
+      <c r="C1391" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1391" s="26" t="str">
+        <f t="shared" si="39"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1391">
+        <v>1048</v>
+      </c>
+      <c r="F1391" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1391" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1392" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1392" s="2">
+        <v>46056</v>
+      </c>
+      <c r="C1392" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1392" s="26" t="str">
+        <f t="shared" si="39"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1392">
+        <v>136</v>
+      </c>
+      <c r="F1392" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1392" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1393" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1393" s="2">
+        <v>46056</v>
+      </c>
+      <c r="C1393" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1393" s="26" t="str">
+        <f t="shared" si="39"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="F1393" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1393" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1394" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1394" s="2">
+        <v>46056</v>
+      </c>
+      <c r="C1394" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1394" s="26" t="str">
+        <f t="shared" si="39"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1394">
+        <v>1176</v>
+      </c>
+      <c r="F1394" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1394" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1395" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1395" s="2">
+        <v>46056</v>
+      </c>
+      <c r="C1395" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1395" s="26" t="str">
+        <f t="shared" si="39"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1395">
+        <v>2288</v>
+      </c>
+      <c r="F1395" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1395" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1396" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1396" s="2">
+        <v>46056</v>
+      </c>
+      <c r="C1396" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1396" s="26" t="str">
+        <f t="shared" si="39"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1396">
+        <v>7055</v>
+      </c>
+      <c r="F1396" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1396" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1397" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1397" s="2">
+        <v>46056</v>
+      </c>
+      <c r="C1397" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1397" s="26" t="str">
+        <f t="shared" si="39"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="F1397" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1397" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1398" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1398" s="2">
+        <v>46056</v>
+      </c>
+      <c r="C1398" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1398" s="26" t="str">
+        <f t="shared" si="39"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1398">
+        <v>5333.4</v>
+      </c>
+      <c r="F1398" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1398" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1399" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1399" s="2">
+        <v>46056</v>
+      </c>
+      <c r="C1399" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1399" s="26" t="str">
+        <f t="shared" si="39"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1399">
+        <v>5881.2</v>
+      </c>
+      <c r="F1399" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1399" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1400" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1400" s="2">
+        <v>46056</v>
+      </c>
+      <c r="C1400" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1400" s="26" t="str">
+        <f t="shared" si="39"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1400">
+        <v>13467.6</v>
+      </c>
+      <c r="F1400" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1400" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1401" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1401" s="2">
+        <v>46056</v>
+      </c>
+      <c r="C1401" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1401" s="26" t="str">
+        <f t="shared" si="39"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1401">
+        <v>13352</v>
+      </c>
+      <c r="F1401" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1401" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1402" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1402" s="2">
+        <v>46056</v>
+      </c>
+      <c r="C1402" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1402" s="26" t="str">
+        <f t="shared" si="39"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1402">
+        <v>2741</v>
+      </c>
+      <c r="F1402" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1402" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1403" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1403" s="2">
+        <v>46056</v>
+      </c>
+      <c r="C1403" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1403" s="26" t="str">
+        <f t="shared" si="39"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1403">
+        <v>2361</v>
+      </c>
+      <c r="F1403" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1403" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1404" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1404" s="2">
+        <v>46056</v>
+      </c>
+      <c r="C1404" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1404" s="26" t="str">
+        <f t="shared" si="39"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1404">
+        <v>2143</v>
+      </c>
+      <c r="F1404" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1404" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1405" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1405" s="2">
+        <v>46057</v>
+      </c>
+      <c r="C1405" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1405" s="26" t="str">
+        <f t="shared" ref="D1405:D1420" si="40">TEXT(B1405, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1405">
+        <v>5370.2</v>
+      </c>
+      <c r="F1405" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1405" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1406" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1406" s="2">
+        <v>46057</v>
+      </c>
+      <c r="C1406" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1406" s="26" t="str">
+        <f t="shared" si="40"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1406">
+        <v>4550</v>
+      </c>
+      <c r="F1406" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1406" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1407" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1407" s="2">
+        <v>46057</v>
+      </c>
+      <c r="C1407" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1407" s="26" t="str">
+        <f t="shared" si="40"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1407">
+        <v>2061</v>
+      </c>
+      <c r="F1407" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1407" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1408" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1408" s="2">
+        <v>46057</v>
+      </c>
+      <c r="C1408" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1408" s="26" t="str">
+        <f t="shared" si="40"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1408">
+        <v>110</v>
+      </c>
+      <c r="F1408" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1408" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1409" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1409" s="2">
+        <v>46057</v>
+      </c>
+      <c r="C1409" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1409" s="26" t="str">
+        <f t="shared" si="40"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="F1409" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1409" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1410" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1410" s="2">
+        <v>46057</v>
+      </c>
+      <c r="C1410" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1410" s="26" t="str">
+        <f t="shared" si="40"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1410">
+        <v>2007.4</v>
+      </c>
+      <c r="F1410" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1410" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1411" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1411" s="2">
+        <v>46057</v>
+      </c>
+      <c r="C1411" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1411" s="26" t="str">
+        <f t="shared" si="40"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1411">
+        <v>2762.2</v>
+      </c>
+      <c r="F1411" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1411" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1412" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1412" s="2">
+        <v>46057</v>
+      </c>
+      <c r="C1412" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1412" s="26" t="str">
+        <f t="shared" si="40"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1412">
+        <v>11792</v>
+      </c>
+      <c r="F1412" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1412" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1413" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1413" s="2">
+        <v>46057</v>
+      </c>
+      <c r="C1413" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1413" s="26" t="str">
+        <f t="shared" si="40"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="F1413" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1413" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1414" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1414" s="2">
+        <v>46057</v>
+      </c>
+      <c r="C1414" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1414" s="26" t="str">
+        <f t="shared" si="40"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="F1414" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1414" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1415" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1415" s="2">
+        <v>46057</v>
+      </c>
+      <c r="C1415" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1415" s="26" t="str">
+        <f t="shared" si="40"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1415">
+        <v>7420.4</v>
+      </c>
+      <c r="F1415" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1415" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1416" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1416" s="2">
+        <v>46057</v>
+      </c>
+      <c r="C1416" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1416" s="26" t="str">
+        <f t="shared" si="40"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="F1416" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1416" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1417" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1417" s="2">
+        <v>46057</v>
+      </c>
+      <c r="C1417" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1417" s="26" t="str">
+        <f t="shared" si="40"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1417">
+        <v>14498.8</v>
+      </c>
+      <c r="F1417" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1417" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1418" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1418" s="2">
+        <v>46057</v>
+      </c>
+      <c r="C1418" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1418" s="26" t="str">
+        <f t="shared" si="40"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1418">
+        <v>3093</v>
+      </c>
+      <c r="F1418" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1418" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1419" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1419" s="2">
+        <v>46057</v>
+      </c>
+      <c r="C1419" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1419" s="26" t="str">
+        <f t="shared" si="40"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1419">
+        <v>5393</v>
+      </c>
+      <c r="F1419" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1419" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1420" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1420" s="2">
+        <v>46057</v>
+      </c>
+      <c r="C1420" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1420" s="26" t="str">
+        <f t="shared" si="40"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1420">
+        <v>3990</v>
+      </c>
+      <c r="F1420" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1420" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1421" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1421" s="2">
+        <v>46058</v>
+      </c>
+      <c r="C1421" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1421" s="26" t="str">
+        <f t="shared" ref="D1421:D1436" si="41">TEXT(B1421, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E1421">
+        <v>2577.6</v>
+      </c>
+      <c r="F1421" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1421" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1422" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1422" s="2">
+        <v>46058</v>
+      </c>
+      <c r="C1422" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1422" s="26" t="str">
+        <f t="shared" si="41"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1422">
+        <v>7062</v>
+      </c>
+      <c r="F1422" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1422" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1423" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1423" s="2">
+        <v>46058</v>
+      </c>
+      <c r="C1423" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1423" s="26" t="str">
+        <f t="shared" si="41"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1423">
+        <v>2010</v>
+      </c>
+      <c r="F1423" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1423" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1424" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1424" s="2">
+        <v>46058</v>
+      </c>
+      <c r="C1424" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1424" s="26" t="str">
+        <f t="shared" si="41"/>
+        <v>Thursday</v>
+      </c>
+      <c r="F1424" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1424" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1425" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1425" s="2">
+        <v>46058</v>
+      </c>
+      <c r="C1425" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1425" s="26" t="str">
+        <f t="shared" si="41"/>
+        <v>Thursday</v>
+      </c>
+      <c r="F1425" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1425" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1426" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1426" s="2">
+        <v>46058</v>
+      </c>
+      <c r="C1426" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1426" s="26" t="str">
+        <f t="shared" si="41"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1426">
+        <v>2357.8000000000002</v>
+      </c>
+      <c r="F1426" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1426" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1427" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1427" s="2">
+        <v>46058</v>
+      </c>
+      <c r="C1427" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1427" s="26" t="str">
+        <f t="shared" si="41"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1427">
+        <v>1758</v>
+      </c>
+      <c r="F1427" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1427" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1428" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1428" s="2">
+        <v>46058</v>
+      </c>
+      <c r="C1428" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1428" s="26" t="str">
+        <f t="shared" si="41"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1428">
+        <v>9568</v>
+      </c>
+      <c r="F1428" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1428" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1429" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1429" s="2">
+        <v>46058</v>
+      </c>
+      <c r="C1429" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1429" s="26" t="str">
+        <f t="shared" si="41"/>
+        <v>Thursday</v>
+      </c>
+      <c r="F1429" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1429" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1430" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1430" s="2">
+        <v>46058</v>
+      </c>
+      <c r="C1430" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1430" s="26" t="str">
+        <f t="shared" si="41"/>
+        <v>Thursday</v>
+      </c>
+      <c r="F1430" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1430" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1431" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1431" s="2">
+        <v>46058</v>
+      </c>
+      <c r="C1431" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1431" s="26" t="str">
+        <f t="shared" si="41"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1431">
+        <v>9464.9</v>
+      </c>
+      <c r="F1431" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1431" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1432" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1432" s="2">
+        <v>46058</v>
+      </c>
+      <c r="C1432" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1432" s="26" t="str">
+        <f t="shared" si="41"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1432">
+        <v>10030.799999999999</v>
+      </c>
+      <c r="F1432" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1432" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1433" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1433" s="2">
+        <v>46058</v>
+      </c>
+      <c r="C1433" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1433" s="26" t="str">
+        <f t="shared" si="41"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1433">
+        <v>11551.5</v>
+      </c>
+      <c r="F1433" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1433" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1434" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1434" s="2">
+        <v>46058</v>
+      </c>
+      <c r="C1434" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1434" s="26" t="str">
+        <f t="shared" si="41"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1434">
+        <v>8993</v>
+      </c>
+      <c r="F1434" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1434" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1435" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1435" s="2">
+        <v>46058</v>
+      </c>
+      <c r="C1435" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1435" s="26" t="str">
+        <f t="shared" si="41"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1435">
+        <v>2177</v>
+      </c>
+      <c r="F1435" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1435" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1436" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1436" s="2">
+        <v>46058</v>
+      </c>
+      <c r="C1436" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1436" s="26" t="str">
+        <f t="shared" si="41"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1436">
+        <v>1944</v>
+      </c>
+      <c r="F1436" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1436" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1437" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1437" s="2">
+        <v>46059</v>
+      </c>
+      <c r="C1437" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1437" s="26" t="str">
+        <f t="shared" ref="D1437:D1452" si="42">TEXT(B1437, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="E1437">
+        <v>4872.3999999999996</v>
+      </c>
+      <c r="F1437" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1437" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1438" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1438" s="2">
+        <v>46059</v>
+      </c>
+      <c r="C1438" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1438" s="26" t="str">
+        <f t="shared" si="42"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1438">
+        <v>5062</v>
+      </c>
+      <c r="F1438" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1438" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1439" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1439" s="2">
+        <v>46059</v>
+      </c>
+      <c r="C1439" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1439" s="26" t="str">
+        <f t="shared" si="42"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1439">
+        <v>2338</v>
+      </c>
+      <c r="F1439" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1439" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1440" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1440" s="2">
+        <v>46059</v>
+      </c>
+      <c r="C1440" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1440" s="26" t="str">
+        <f t="shared" si="42"/>
+        <v>Friday</v>
+      </c>
+      <c r="F1440" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1440" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1441" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1441" s="2">
+        <v>46059</v>
+      </c>
+      <c r="C1441" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1441" s="26" t="str">
+        <f t="shared" si="42"/>
+        <v>Friday</v>
+      </c>
+      <c r="F1441" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1441" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1442" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1442" s="2">
+        <v>46059</v>
+      </c>
+      <c r="C1442" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1442" s="26" t="str">
+        <f t="shared" si="42"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1442">
+        <v>2938.3</v>
+      </c>
+      <c r="F1442" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1442" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1443" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1443" s="2">
+        <v>46059</v>
+      </c>
+      <c r="C1443" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1443" s="26" t="str">
+        <f t="shared" si="42"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1443">
+        <v>4841</v>
+      </c>
+      <c r="F1443" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1443" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1444" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1444" s="2">
+        <v>46059</v>
+      </c>
+      <c r="C1444" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1444" s="26" t="str">
+        <f t="shared" si="42"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1444">
+        <v>7356</v>
+      </c>
+      <c r="F1444" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1444" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1445" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1445" s="2">
+        <v>46059</v>
+      </c>
+      <c r="C1445" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1445" s="26" t="str">
+        <f t="shared" si="42"/>
+        <v>Friday</v>
+      </c>
+      <c r="F1445" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1445" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1446" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1446" s="2">
+        <v>46059</v>
+      </c>
+      <c r="C1446" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1446" s="26" t="str">
+        <f t="shared" si="42"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1446">
+        <v>4753.6000000000004</v>
+      </c>
+      <c r="F1446" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1446" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1447" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1447" s="2">
+        <v>46059</v>
+      </c>
+      <c r="C1447" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1447" s="26" t="str">
+        <f t="shared" si="42"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1447">
+        <v>6707.4</v>
+      </c>
+      <c r="F1447" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1447" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1448" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1448" s="2">
+        <v>46059</v>
+      </c>
+      <c r="C1448" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1448" s="26" t="str">
+        <f t="shared" si="42"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1448">
+        <v>12092</v>
+      </c>
+      <c r="F1448" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1448" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1449" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1449" s="2">
+        <v>46059</v>
+      </c>
+      <c r="C1449" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1449" s="26" t="str">
+        <f t="shared" si="42"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1449">
+        <v>18622.400000000001</v>
+      </c>
+      <c r="F1449" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1449" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1450" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1450" s="2">
+        <v>46059</v>
+      </c>
+      <c r="C1450" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1450" s="26" t="str">
+        <f t="shared" si="42"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1450">
+        <v>7125</v>
+      </c>
+      <c r="F1450" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1450" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1451" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1451" s="2">
+        <v>46059</v>
+      </c>
+      <c r="C1451" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1451" s="26" t="str">
+        <f t="shared" si="42"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1451">
+        <v>5035</v>
+      </c>
+      <c r="F1451" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1451" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1452" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1452" s="2">
+        <v>46059</v>
+      </c>
+      <c r="C1452" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1452" s="26" t="str">
+        <f t="shared" si="42"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1452">
+        <v>3304</v>
+      </c>
+      <c r="F1452" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1452" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1453" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1453" s="2">
+        <v>46062</v>
+      </c>
+      <c r="C1453" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1453" s="26" t="str">
+        <f t="shared" ref="D1453:D1468" si="43">TEXT(B1453, "dddd")</f>
+        <v>Monday</v>
+      </c>
+      <c r="E1453">
+        <v>6231.2</v>
+      </c>
+      <c r="F1453" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1453" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1454" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1454" s="2">
+        <v>46062</v>
+      </c>
+      <c r="C1454" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1454" s="26" t="str">
+        <f t="shared" si="43"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1454">
+        <v>9366</v>
+      </c>
+      <c r="F1454" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1454" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1455" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1455" s="2">
+        <v>46062</v>
+      </c>
+      <c r="C1455" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1455" s="26" t="str">
+        <f t="shared" si="43"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1455">
+        <v>1620</v>
+      </c>
+      <c r="F1455" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1455" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1456" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1456" s="2">
+        <v>46062</v>
+      </c>
+      <c r="C1456" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1456" s="26" t="str">
+        <f t="shared" si="43"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1456">
+        <v>194.8</v>
+      </c>
+      <c r="F1456" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1456" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1457" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1457" s="2">
+        <v>46062</v>
+      </c>
+      <c r="C1457" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1457" s="26" t="str">
+        <f t="shared" si="43"/>
+        <v>Monday</v>
+      </c>
+      <c r="F1457" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1457" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1458" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1458" s="2">
+        <v>46062</v>
+      </c>
+      <c r="C1458" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1458" s="26" t="str">
+        <f t="shared" si="43"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1458">
+        <v>2161.6</v>
+      </c>
+      <c r="F1458" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1458" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1459" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1459" s="2">
+        <v>46062</v>
+      </c>
+      <c r="C1459" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1459" s="26" t="str">
+        <f t="shared" si="43"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1459">
+        <v>5256</v>
+      </c>
+      <c r="F1459" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1459" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1460" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1460" s="2">
+        <v>46062</v>
+      </c>
+      <c r="C1460" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1460" s="26" t="str">
+        <f t="shared" si="43"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1460">
+        <v>12320</v>
+      </c>
+      <c r="F1460" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1460" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1461" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1461" s="2">
+        <v>46062</v>
+      </c>
+      <c r="C1461" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1461" s="26" t="str">
+        <f t="shared" si="43"/>
+        <v>Monday</v>
+      </c>
+      <c r="F1461" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1461" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1462" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1462" s="2">
+        <v>46062</v>
+      </c>
+      <c r="C1462" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1462" s="26" t="str">
+        <f t="shared" si="43"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1462">
+        <v>3492.8</v>
+      </c>
+      <c r="F1462" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1462" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1463" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1463" s="2">
+        <v>46062</v>
+      </c>
+      <c r="C1463" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1463" s="26" t="str">
+        <f t="shared" si="43"/>
+        <v>Monday</v>
+      </c>
+      <c r="F1463" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1463" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1464" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1464" s="2">
+        <v>46062</v>
+      </c>
+      <c r="C1464" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1464" s="26" t="str">
+        <f t="shared" si="43"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1464">
+        <v>13244</v>
+      </c>
+      <c r="F1464" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1464" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1465" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1465" s="2">
+        <v>46062</v>
+      </c>
+      <c r="C1465" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1465" s="26" t="str">
+        <f t="shared" si="43"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1465">
+        <v>19002.400000000001</v>
+      </c>
+      <c r="F1465" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1465" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1466" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1466" s="2">
+        <v>46062</v>
+      </c>
+      <c r="C1466" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1466" s="26" t="str">
+        <f t="shared" si="43"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1466">
+        <v>10015</v>
+      </c>
+      <c r="F1466" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1466" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1467" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1467" s="2">
+        <v>46062</v>
+      </c>
+      <c r="C1467" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1467" s="26" t="str">
+        <f t="shared" si="43"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1467">
+        <v>3378</v>
+      </c>
+      <c r="F1467" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1467" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1468" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1468" s="2">
+        <v>46062</v>
+      </c>
+      <c r="C1468" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1468" s="26" t="str">
+        <f t="shared" si="43"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1468">
+        <v>2110</v>
+      </c>
+      <c r="F1468" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1468" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1469" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1469" s="2">
+        <v>46063</v>
+      </c>
+      <c r="C1469" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1469" s="26" t="str">
+        <f t="shared" ref="D1469:D1484" si="44">TEXT(B1469, "dddd")</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1469">
+        <v>5799</v>
+      </c>
+      <c r="F1469" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1469" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1470" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1470" s="2">
+        <v>46063</v>
+      </c>
+      <c r="C1470" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1470" s="26" t="str">
+        <f t="shared" si="44"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1470">
+        <v>5604</v>
+      </c>
+      <c r="F1470" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1470" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1471" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1471" s="2">
+        <v>46063</v>
+      </c>
+      <c r="C1471" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1471" s="26" t="str">
+        <f t="shared" si="44"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1471">
+        <v>3414</v>
+      </c>
+      <c r="F1471" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1471" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1472" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1472" s="2">
+        <v>46063</v>
+      </c>
+      <c r="C1472" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1472" s="26" t="str">
+        <f t="shared" si="44"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="F1472" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1472" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1473" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1473" s="2">
+        <v>46063</v>
+      </c>
+      <c r="C1473" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1473" s="26" t="str">
+        <f t="shared" si="44"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="F1473" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1473" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1474" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1474" s="2">
+        <v>46063</v>
+      </c>
+      <c r="C1474" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1474" s="26" t="str">
+        <f t="shared" si="44"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1474">
+        <v>2824</v>
+      </c>
+      <c r="F1474" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1474" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1475" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1475" s="2">
+        <v>46063</v>
+      </c>
+      <c r="C1475" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1475" s="26" t="str">
+        <f t="shared" si="44"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1475">
+        <v>4238</v>
+      </c>
+      <c r="F1475" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1475" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1476" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1476" s="2">
+        <v>46063</v>
+      </c>
+      <c r="C1476" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1476" s="26" t="str">
+        <f t="shared" si="44"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1476">
+        <v>2979</v>
+      </c>
+      <c r="F1476" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1476" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1477" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1477" s="2">
+        <v>46063</v>
+      </c>
+      <c r="C1477" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1477" s="26" t="str">
+        <f t="shared" si="44"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="F1477" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1477" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1478" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1478" s="2">
+        <v>46063</v>
+      </c>
+      <c r="C1478" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1478" s="26" t="str">
+        <f t="shared" si="44"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1478">
+        <v>4399</v>
+      </c>
+      <c r="F1478" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1478" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1479" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1479" s="2">
+        <v>46063</v>
+      </c>
+      <c r="C1479" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1479" s="26" t="str">
+        <f t="shared" si="44"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1479">
+        <v>7631.8</v>
+      </c>
+      <c r="F1479" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1479" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1480" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1480" s="2">
+        <v>46063</v>
+      </c>
+      <c r="C1480" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1480" s="26" t="str">
+        <f t="shared" si="44"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1480">
+        <v>11642.4</v>
+      </c>
+      <c r="F1480" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1480" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1481" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1481" s="2">
+        <v>46063</v>
+      </c>
+      <c r="C1481" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1481" s="26" t="str">
+        <f t="shared" si="44"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1481">
+        <v>7472.2</v>
+      </c>
+      <c r="F1481" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1481" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1482" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1482" s="2">
+        <v>46063</v>
+      </c>
+      <c r="C1482" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1482" s="26" t="str">
+        <f t="shared" si="44"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1482">
+        <v>9264</v>
+      </c>
+      <c r="F1482" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1482" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1483" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1483" s="2">
+        <v>46063</v>
+      </c>
+      <c r="C1483" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1483" s="26" t="str">
+        <f t="shared" si="44"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="F1483" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1483" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1484" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1484" s="2">
+        <v>46063</v>
+      </c>
+      <c r="C1484" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1484" s="26" t="str">
+        <f t="shared" si="44"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1484">
+        <v>3248</v>
+      </c>
+      <c r="F1484" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1484" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1485" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1485" s="2">
+        <v>46064</v>
+      </c>
+      <c r="C1485" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1485" s="26" t="str">
+        <f t="shared" ref="D1485:D1500" si="45">TEXT(B1485, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1485">
+        <v>1974.8</v>
+      </c>
+      <c r="F1485" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1485" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1486" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1486" s="2">
+        <v>46064</v>
+      </c>
+      <c r="C1486" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1486" s="26" t="str">
+        <f t="shared" si="45"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1486">
+        <v>2666</v>
+      </c>
+      <c r="F1486" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1486" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1487" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1487" s="2">
+        <v>46064</v>
+      </c>
+      <c r="C1487" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1487" s="26" t="str">
+        <f t="shared" si="45"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1487">
+        <v>1820</v>
+      </c>
+      <c r="F1487" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1487" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1488" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1488" s="2">
+        <v>46064</v>
+      </c>
+      <c r="C1488" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1488" s="26" t="str">
+        <f t="shared" si="45"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1488">
+        <v>190.4</v>
+      </c>
+      <c r="F1488" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1488" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1489" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1489" s="2">
+        <v>46064</v>
+      </c>
+      <c r="C1489" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1489" s="26" t="str">
+        <f t="shared" si="45"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="F1489" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1489" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1490" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1490" s="2">
+        <v>46064</v>
+      </c>
+      <c r="C1490" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1490" s="26" t="str">
+        <f t="shared" si="45"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1490">
+        <v>3898.2</v>
+      </c>
+      <c r="F1490" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1490" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1491" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1491" s="2">
+        <v>46064</v>
+      </c>
+      <c r="C1491" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1491" s="26" t="str">
+        <f t="shared" si="45"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1491">
+        <v>3611.8</v>
+      </c>
+      <c r="F1491" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1491" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1492" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1492" s="2">
+        <v>46064</v>
+      </c>
+      <c r="C1492" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1492" s="26" t="str">
+        <f t="shared" si="45"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1492">
+        <v>4361</v>
+      </c>
+      <c r="F1492" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1492" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1493" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1493" s="2">
+        <v>46064</v>
+      </c>
+      <c r="C1493" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1493" s="26" t="str">
+        <f t="shared" si="45"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="F1493" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1493" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1494" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1494" s="2">
+        <v>46064</v>
+      </c>
+      <c r="C1494" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1494" s="26" t="str">
+        <f t="shared" si="45"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1494">
+        <v>6098.2</v>
+      </c>
+      <c r="F1494" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1494" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1495" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1495" s="2">
+        <v>46064</v>
+      </c>
+      <c r="C1495" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1495" s="26" t="str">
+        <f t="shared" si="45"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1495">
+        <v>6497.7</v>
+      </c>
+      <c r="F1495" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1495" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1496" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1496" s="2">
+        <v>46064</v>
+      </c>
+      <c r="C1496" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1496" s="26" t="str">
+        <f t="shared" si="45"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="F1496" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1496" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1497" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1497" s="2">
+        <v>46064</v>
+      </c>
+      <c r="C1497" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1497" s="26" t="str">
+        <f t="shared" si="45"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1497">
+        <v>14230.2</v>
+      </c>
+      <c r="F1497" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1497" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1498" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1498" s="2">
+        <v>46064</v>
+      </c>
+      <c r="C1498" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1498" s="26" t="str">
+        <f t="shared" si="45"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1498">
+        <v>2607</v>
+      </c>
+      <c r="F1498" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1498" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1499" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1499" s="2">
+        <v>46064</v>
+      </c>
+      <c r="C1499" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1499" s="26" t="str">
+        <f t="shared" si="45"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="F1499" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1499" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1500" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1500" s="2">
+        <v>46064</v>
+      </c>
+      <c r="C1500" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1500" s="26" t="str">
+        <f t="shared" si="45"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1500">
+        <v>3119</v>
+      </c>
+      <c r="F1500" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1500" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1501" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1501" s="2">
+        <v>46065</v>
+      </c>
+      <c r="C1501" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1501" s="26" t="str">
+        <f t="shared" ref="D1501:D1516" si="46">TEXT(B1501, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E1501">
+        <v>3119</v>
+      </c>
+      <c r="F1501" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1501" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1502" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1502" s="2">
+        <v>46065</v>
+      </c>
+      <c r="C1502" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1502" s="26" t="str">
+        <f t="shared" si="46"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1502">
+        <v>3300</v>
+      </c>
+      <c r="F1502" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1502" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1503" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1503" s="2">
+        <v>46065</v>
+      </c>
+      <c r="C1503" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1503" s="26" t="str">
+        <f t="shared" si="46"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1503">
+        <v>2433</v>
+      </c>
+      <c r="F1503" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1503" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1504" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1504" s="2">
+        <v>46065</v>
+      </c>
+      <c r="C1504" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1504" s="26" t="str">
+        <f t="shared" si="46"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1504">
+        <v>144</v>
+      </c>
+      <c r="F1504" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1504" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1505" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1505" s="2">
+        <v>46065</v>
+      </c>
+      <c r="C1505" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1505" s="26" t="str">
+        <f t="shared" si="46"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1505">
+        <v>2134</v>
+      </c>
+      <c r="F1505" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1505" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1506" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1506" s="2">
+        <v>46065</v>
+      </c>
+      <c r="C1506" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1506" s="26" t="str">
+        <f t="shared" si="46"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1506">
+        <v>1382</v>
+      </c>
+      <c r="F1506" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1506" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1507" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1507" s="2">
+        <v>46065</v>
+      </c>
+      <c r="C1507" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1507" s="26" t="str">
+        <f t="shared" si="46"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1507">
+        <v>5444</v>
+      </c>
+      <c r="F1507" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1507" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1508" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1508" s="2">
+        <v>46065</v>
+      </c>
+      <c r="C1508" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1508" s="26" t="str">
+        <f t="shared" si="46"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1508">
+        <v>4395</v>
+      </c>
+      <c r="F1508" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1508" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1509" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1509" s="2">
+        <v>46065</v>
+      </c>
+      <c r="C1509" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1509" s="26" t="str">
+        <f t="shared" si="46"/>
+        <v>Thursday</v>
+      </c>
+      <c r="F1509" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1509" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1510" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1510" s="2">
+        <v>46065</v>
+      </c>
+      <c r="C1510" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1510" s="26" t="str">
+        <f t="shared" si="46"/>
+        <v>Thursday</v>
+      </c>
+      <c r="F1510" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1510" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1511" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1511" s="2">
+        <v>46065</v>
+      </c>
+      <c r="C1511" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1511" s="26" t="str">
+        <f t="shared" si="46"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1511">
+        <v>5555</v>
+      </c>
+      <c r="F1511" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1511" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1512" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1512" s="2">
+        <v>46065</v>
+      </c>
+      <c r="C1512" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1512" s="26" t="str">
+        <f t="shared" si="46"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1512">
+        <v>13690</v>
+      </c>
+      <c r="F1512" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1512" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1513" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1513" s="2">
+        <v>46065</v>
+      </c>
+      <c r="C1513" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1513" s="26" t="str">
+        <f t="shared" si="46"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1513">
+        <v>18705</v>
+      </c>
+      <c r="F1513" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1513" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1514" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1514" s="2">
+        <v>46065</v>
+      </c>
+      <c r="C1514" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1514" s="26" t="str">
+        <f t="shared" si="46"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1514">
+        <v>3853</v>
+      </c>
+      <c r="F1514" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1514" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1515" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1515" s="2">
+        <v>46065</v>
+      </c>
+      <c r="C1515" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1515" s="26" t="str">
+        <f t="shared" si="46"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1515">
+        <v>4069</v>
+      </c>
+      <c r="F1515" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1515" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1516" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1516" s="2">
+        <v>46065</v>
+      </c>
+      <c r="C1516" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1516" s="26" t="str">
+        <f t="shared" si="46"/>
+        <v>Thursday</v>
+      </c>
+      <c r="F1516" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1516" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1517" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1517" s="2">
+        <v>46066</v>
+      </c>
+      <c r="C1517" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1517" s="26" t="str">
+        <f t="shared" ref="D1517:D1532" si="47">TEXT(B1517, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="F1517" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1517" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1518" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1518" s="2">
+        <v>46066</v>
+      </c>
+      <c r="C1518" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1518" s="26" t="str">
+        <f t="shared" si="47"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1518">
+        <v>5529</v>
+      </c>
+      <c r="F1518" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1518" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1519" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1519" s="2">
+        <v>46066</v>
+      </c>
+      <c r="C1519" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1519" s="26" t="str">
+        <f t="shared" si="47"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1519">
+        <v>4176</v>
+      </c>
+      <c r="F1519" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1519" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1520" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1520" s="2">
+        <v>46066</v>
+      </c>
+      <c r="C1520" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1520" s="26" t="str">
+        <f t="shared" si="47"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1520">
+        <v>212</v>
+      </c>
+      <c r="F1520" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1520" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1521" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1521" s="2">
+        <v>46066</v>
+      </c>
+      <c r="C1521" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1521" s="26" t="str">
+        <f t="shared" si="47"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1521">
+        <v>736</v>
+      </c>
+      <c r="F1521" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1521" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1522" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1522" s="2">
+        <v>46066</v>
+      </c>
+      <c r="C1522" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1522" s="26" t="str">
+        <f t="shared" si="47"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1522">
+        <v>2896</v>
+      </c>
+      <c r="F1522" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1522" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1523" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1523" s="2">
+        <v>46066</v>
+      </c>
+      <c r="C1523" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1523" s="26" t="str">
+        <f t="shared" si="47"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1523">
+        <v>5349</v>
+      </c>
+      <c r="F1523" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1523" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1524" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1524" s="2">
+        <v>46066</v>
+      </c>
+      <c r="C1524" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1524" s="26" t="str">
+        <f t="shared" si="47"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1524">
+        <v>2510</v>
+      </c>
+      <c r="F1524" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1524" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1525" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1525" s="2">
+        <v>46066</v>
+      </c>
+      <c r="C1525" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1525" s="26" t="str">
+        <f t="shared" si="47"/>
+        <v>Friday</v>
+      </c>
+      <c r="F1525" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1525" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1526" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1526" s="2">
+        <v>46066</v>
+      </c>
+      <c r="C1526" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1526" s="26" t="str">
+        <f t="shared" si="47"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1526">
+        <v>2729</v>
+      </c>
+      <c r="F1526" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1526" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1527" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1527" s="2">
+        <v>46066</v>
+      </c>
+      <c r="C1527" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1527" s="26" t="str">
+        <f t="shared" si="47"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1527">
+        <v>5136</v>
+      </c>
+      <c r="F1527" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1527" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1528" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1528" s="2">
+        <v>46066</v>
+      </c>
+      <c r="C1528" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1528" s="26" t="str">
+        <f t="shared" si="47"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1528">
+        <v>13225</v>
+      </c>
+      <c r="F1528" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1528" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1529" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1529" s="2">
+        <v>46066</v>
+      </c>
+      <c r="C1529" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1529" s="26" t="str">
+        <f t="shared" si="47"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1529">
+        <v>18714</v>
+      </c>
+      <c r="F1529" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1529" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1530" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1530" s="2">
+        <v>46066</v>
+      </c>
+      <c r="C1530" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1530" s="26" t="str">
+        <f t="shared" si="47"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1530">
+        <v>2890</v>
+      </c>
+      <c r="F1530" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1530" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1531" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1531" s="2">
+        <v>46066</v>
+      </c>
+      <c r="C1531" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1531" s="26" t="str">
+        <f t="shared" si="47"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1531">
+        <v>1269</v>
+      </c>
+      <c r="F1531" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1531" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1532" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1532" s="2">
+        <v>46066</v>
+      </c>
+      <c r="C1532" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1532" s="26" t="str">
+        <f t="shared" si="47"/>
+        <v>Friday</v>
+      </c>
+      <c r="F1532" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1532" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1533" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1533" s="2">
+        <v>46069</v>
+      </c>
+      <c r="C1533" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1533" s="26" t="str">
+        <f t="shared" ref="D1533:D1548" si="48">TEXT(B1533, "dddd")</f>
+        <v>Monday</v>
+      </c>
+      <c r="E1533">
+        <v>2369</v>
+      </c>
+      <c r="F1533" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1533" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1534" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1534" s="2">
+        <v>46069</v>
+      </c>
+      <c r="C1534" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1534" s="26" t="str">
+        <f t="shared" si="48"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1534">
+        <v>4500</v>
+      </c>
+      <c r="F1534" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1534" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1535" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1535" s="2">
+        <v>46069</v>
+      </c>
+      <c r="C1535" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1535" s="26" t="str">
+        <f t="shared" si="48"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1535">
+        <v>1630</v>
+      </c>
+      <c r="F1535" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1535" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1536" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1536" s="2">
+        <v>46069</v>
+      </c>
+      <c r="C1536" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1536" s="26" t="str">
+        <f t="shared" si="48"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1536">
+        <v>220</v>
+      </c>
+      <c r="F1536" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1536" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1537" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1537" s="2">
+        <v>46069</v>
+      </c>
+      <c r="C1537" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1537" s="26" t="str">
+        <f t="shared" si="48"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1537">
+        <v>2235.6</v>
+      </c>
+      <c r="F1537" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1537" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1538" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1538" s="2">
+        <v>46069</v>
+      </c>
+      <c r="C1538" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1538" s="26" t="str">
+        <f t="shared" si="48"/>
+        <v>Monday</v>
+      </c>
+      <c r="F1538" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1538" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1539" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1539" s="2">
+        <v>46069</v>
+      </c>
+      <c r="C1539" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1539" s="26" t="str">
+        <f t="shared" si="48"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1539">
+        <v>4020</v>
+      </c>
+      <c r="F1539" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1539" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1540" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1540" s="2">
+        <v>46069</v>
+      </c>
+      <c r="C1540" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1540" s="26" t="str">
+        <f t="shared" si="48"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1540">
+        <v>5271</v>
+      </c>
+      <c r="F1540" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1540" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1541" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1541" s="2">
+        <v>46069</v>
+      </c>
+      <c r="C1541" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1541" s="26" t="str">
+        <f t="shared" si="48"/>
+        <v>Monday</v>
+      </c>
+      <c r="F1541" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1541" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1542" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1542" s="2">
+        <v>46069</v>
+      </c>
+      <c r="C1542" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1542" s="26" t="str">
+        <f t="shared" si="48"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1542">
+        <v>2667</v>
+      </c>
+      <c r="F1542" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1542" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1543" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1543" s="2">
+        <v>46069</v>
+      </c>
+      <c r="C1543" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1543" s="26" t="str">
+        <f t="shared" si="48"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1543">
+        <v>3614</v>
+      </c>
+      <c r="F1543" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1543" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1544" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1544" s="2">
+        <v>46069</v>
+      </c>
+      <c r="C1544" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1544" s="26" t="str">
+        <f t="shared" si="48"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1544">
+        <v>9846</v>
+      </c>
+      <c r="F1544" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1544" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1545" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1545" s="2">
+        <v>46069</v>
+      </c>
+      <c r="C1545" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1545" s="26" t="str">
+        <f t="shared" si="48"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1545">
+        <v>15211</v>
+      </c>
+      <c r="F1545" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1545" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1546" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1546" s="2">
+        <v>46069</v>
+      </c>
+      <c r="C1546" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1546" s="26" t="str">
+        <f t="shared" si="48"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1546">
+        <v>2412</v>
+      </c>
+      <c r="F1546" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1546" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1547" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1547" s="2">
+        <v>46069</v>
+      </c>
+      <c r="C1547" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1547" s="26" t="str">
+        <f t="shared" si="48"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1547">
+        <v>2194</v>
+      </c>
+      <c r="F1547" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1547" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1548" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1548" s="2">
+        <v>46069</v>
+      </c>
+      <c r="C1548" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1548" s="26" t="str">
+        <f t="shared" si="48"/>
+        <v>Monday</v>
+      </c>
+      <c r="F1548" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1548" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1549" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1549" s="2">
+        <v>46070</v>
+      </c>
+      <c r="C1549" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1549" s="26" t="str">
+        <f t="shared" ref="D1549:D1564" si="49">TEXT(B1549, "dddd")</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1549">
+        <v>6537</v>
+      </c>
+      <c r="F1549" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1549" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1550" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1550" s="2">
+        <v>46070</v>
+      </c>
+      <c r="C1550" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1550" s="26" t="str">
+        <f t="shared" si="49"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1550">
+        <v>6290</v>
+      </c>
+      <c r="F1550" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1550" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1551" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1551" s="2">
+        <v>46070</v>
+      </c>
+      <c r="C1551" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1551" s="26" t="str">
+        <f t="shared" si="49"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1551">
+        <v>1916</v>
+      </c>
+      <c r="F1551" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1551" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1552" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1552" s="2">
+        <v>46070</v>
+      </c>
+      <c r="C1552" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1552" s="26" t="str">
+        <f t="shared" si="49"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1552">
+        <v>400</v>
+      </c>
+      <c r="F1552" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1552" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1553" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1553" s="2">
+        <v>46070</v>
+      </c>
+      <c r="C1553" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1553" s="26" t="str">
+        <f t="shared" si="49"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="F1553" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1553" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1554" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1554" s="2">
+        <v>46070</v>
+      </c>
+      <c r="C1554" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1554" s="26" t="str">
+        <f t="shared" si="49"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1554">
+        <v>2327</v>
+      </c>
+      <c r="F1554" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1554" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1555" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1555" s="2">
+        <v>46070</v>
+      </c>
+      <c r="C1555" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1555" s="26" t="str">
+        <f t="shared" si="49"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1555">
+        <v>3723</v>
+      </c>
+      <c r="F1555" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1555" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1556" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1556" s="2">
+        <v>46070</v>
+      </c>
+      <c r="C1556" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1556" s="26" t="str">
+        <f t="shared" si="49"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1556">
+        <v>6526</v>
+      </c>
+      <c r="F1556" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1556" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1557" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1557" s="2">
+        <v>46070</v>
+      </c>
+      <c r="C1557" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1557" s="26" t="str">
+        <f t="shared" si="49"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="F1557" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1557" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1558" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1558" s="2">
+        <v>46070</v>
+      </c>
+      <c r="C1558" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1558" s="26" t="str">
+        <f t="shared" si="49"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1558">
+        <v>2838</v>
+      </c>
+      <c r="F1558" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1558" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1559" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1559" s="2">
+        <v>46070</v>
+      </c>
+      <c r="C1559" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1559" s="26" t="str">
+        <f t="shared" si="49"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1559">
+        <v>9072</v>
+      </c>
+      <c r="F1559" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1559" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1560" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1560" s="2">
+        <v>46070</v>
+      </c>
+      <c r="C1560" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1560" s="26" t="str">
+        <f t="shared" si="49"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1560">
+        <v>13015</v>
+      </c>
+      <c r="F1560" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1560" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1561" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1561" s="2">
+        <v>46070</v>
+      </c>
+      <c r="C1561" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1561" s="26" t="str">
+        <f t="shared" si="49"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1561">
+        <v>9406</v>
+      </c>
+      <c r="F1561" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1561" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1562" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1562" s="2">
+        <v>46070</v>
+      </c>
+      <c r="C1562" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1562" s="26" t="str">
+        <f t="shared" si="49"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1562">
+        <v>9727</v>
+      </c>
+      <c r="F1562" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1562" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1563" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1563" s="2">
+        <v>46070</v>
+      </c>
+      <c r="C1563" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1563" s="26" t="str">
+        <f t="shared" si="49"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1563">
+        <v>4129</v>
+      </c>
+      <c r="F1563" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1563" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1564" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1564" s="2">
+        <v>46070</v>
+      </c>
+      <c r="C1564" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1564" s="26" t="str">
+        <f t="shared" si="49"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="F1564" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1564" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1565" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1565" s="2">
+        <v>46071</v>
+      </c>
+      <c r="C1565" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1565" s="26" t="str">
+        <f t="shared" ref="D1565:D1580" si="50">TEXT(B1565, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1565">
+        <v>5086.6000000000004</v>
+      </c>
+      <c r="F1565" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1565" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1566" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1566" s="2">
+        <v>46071</v>
+      </c>
+      <c r="C1566" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1566" s="26" t="str">
+        <f t="shared" si="50"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1566">
+        <v>5827</v>
+      </c>
+      <c r="F1566" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1566" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1567" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1567" s="2">
+        <v>46071</v>
+      </c>
+      <c r="C1567" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1567" s="26" t="str">
+        <f t="shared" si="50"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1567">
+        <v>1314</v>
+      </c>
+      <c r="F1567" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1567" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1568" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1568" s="2">
+        <v>46071</v>
+      </c>
+      <c r="C1568" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1568" s="26" t="str">
+        <f t="shared" si="50"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1568">
+        <v>238</v>
+      </c>
+      <c r="F1568" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1568" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1569" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1569" s="2">
+        <v>46071</v>
+      </c>
+      <c r="C1569" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1569" s="26" t="str">
+        <f t="shared" si="50"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="F1569" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1569" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1570" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1570" s="2">
+        <v>46071</v>
+      </c>
+      <c r="C1570" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1570" s="26" t="str">
+        <f t="shared" si="50"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1570">
+        <v>1633</v>
+      </c>
+      <c r="F1570" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1570" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1571" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1571" s="2">
+        <v>46071</v>
+      </c>
+      <c r="C1571" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1571" s="26" t="str">
+        <f t="shared" si="50"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1571">
+        <v>1926</v>
+      </c>
+      <c r="F1571" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1571" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1572" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1572" s="2">
+        <v>46071</v>
+      </c>
+      <c r="C1572" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1572" s="26" t="str">
+        <f t="shared" si="50"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1572">
+        <v>5397</v>
+      </c>
+      <c r="F1572" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1572" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1573" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1573" s="2">
+        <v>46071</v>
+      </c>
+      <c r="C1573" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1573" s="26" t="str">
+        <f t="shared" si="50"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="F1573" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1573" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1574" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1574" s="2">
+        <v>46071</v>
+      </c>
+      <c r="C1574" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1574" s="26" t="str">
+        <f t="shared" si="50"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1574">
+        <v>540</v>
+      </c>
+      <c r="F1574" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1574" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1575" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1575" s="2">
+        <v>46071</v>
+      </c>
+      <c r="C1575" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1575" s="26" t="str">
+        <f t="shared" si="50"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1575">
+        <v>8796</v>
+      </c>
+      <c r="F1575" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1575" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1576" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1576" s="2">
+        <v>46071</v>
+      </c>
+      <c r="C1576" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1576" s="26" t="str">
+        <f t="shared" si="50"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1576">
+        <v>2979</v>
+      </c>
+      <c r="F1576" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1576" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1577" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1577" s="2">
+        <v>46071</v>
+      </c>
+      <c r="C1577" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1577" s="26" t="str">
+        <f t="shared" si="50"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1577">
+        <v>14342</v>
+      </c>
+      <c r="F1577" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1577" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1578" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1578" s="2">
+        <v>46071</v>
+      </c>
+      <c r="C1578" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1578" s="26" t="str">
+        <f t="shared" si="50"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1578">
+        <v>10209</v>
+      </c>
+      <c r="F1578" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1578" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1579" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1579" s="2">
+        <v>46071</v>
+      </c>
+      <c r="C1579" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1579" s="26" t="str">
+        <f t="shared" si="50"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1579">
+        <v>4444</v>
+      </c>
+      <c r="F1579" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1579" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1580" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1580" s="2">
+        <v>46071</v>
+      </c>
+      <c r="C1580" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1580" s="26" t="str">
+        <f t="shared" si="50"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="F1580" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1580" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1581" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1581" s="2">
+        <v>46072</v>
+      </c>
+      <c r="C1581" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1581" s="26" t="str">
+        <f t="shared" ref="D1581:D1596" si="51">TEXT(B1581, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E1581">
+        <v>4040.6</v>
+      </c>
+      <c r="F1581" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1581" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1582" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1582" s="2">
+        <v>46072</v>
+      </c>
+      <c r="C1582" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1582" s="26" t="str">
+        <f t="shared" si="51"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1582">
+        <v>6002</v>
+      </c>
+      <c r="F1582" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1582" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1583" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1583" s="2">
+        <v>46072</v>
+      </c>
+      <c r="C1583" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1583" s="26" t="str">
+        <f t="shared" si="51"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1583">
+        <v>1926</v>
+      </c>
+      <c r="F1583" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1583" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1584" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1584" s="2">
+        <v>46072</v>
+      </c>
+      <c r="C1584" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1584" s="26" t="str">
+        <f t="shared" si="51"/>
+        <v>Thursday</v>
+      </c>
+      <c r="F1584" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1584" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1585" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1585" s="2">
+        <v>46072</v>
+      </c>
+      <c r="C1585" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1585" s="26" t="str">
+        <f t="shared" si="51"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1585">
+        <v>2109.4</v>
+      </c>
+      <c r="F1585" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1585" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1586" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1586" s="2">
+        <v>46072</v>
+      </c>
+      <c r="C1586" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1586" s="26" t="str">
+        <f t="shared" si="51"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1586">
+        <v>2446</v>
+      </c>
+      <c r="F1586" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1586" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1587" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1587" s="2">
+        <v>46072</v>
+      </c>
+      <c r="C1587" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1587" s="26" t="str">
+        <f t="shared" si="51"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1587">
+        <v>1284</v>
+      </c>
+      <c r="F1587" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1587" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1588" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1588" s="2">
+        <v>46072</v>
+      </c>
+      <c r="C1588" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1588" s="26" t="str">
+        <f t="shared" si="51"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1588">
+        <v>8704</v>
+      </c>
+      <c r="F1588" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1588" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1589" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1589" s="2">
+        <v>46072</v>
+      </c>
+      <c r="C1589" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1589" s="26" t="str">
+        <f t="shared" si="51"/>
+        <v>Thursday</v>
+      </c>
+      <c r="F1589" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1589" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1590" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1590" s="2">
+        <v>46072</v>
+      </c>
+      <c r="C1590" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1590" s="26" t="str">
+        <f t="shared" si="51"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1590">
+        <v>3838</v>
+      </c>
+      <c r="F1590" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1590" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1591" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1591" s="2">
+        <v>46072</v>
+      </c>
+      <c r="C1591" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1591" s="26" t="str">
+        <f t="shared" si="51"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1591">
+        <v>6867</v>
+      </c>
+      <c r="F1591" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1591" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1592" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1592" s="2">
+        <v>46072</v>
+      </c>
+      <c r="C1592" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1592" s="26" t="str">
+        <f t="shared" si="51"/>
+        <v>Thursday</v>
+      </c>
+      <c r="F1592" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1592" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1593" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1593" s="2">
+        <v>46072</v>
+      </c>
+      <c r="C1593" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1593" s="26" t="str">
+        <f t="shared" si="51"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1593">
+        <v>21248</v>
+      </c>
+      <c r="F1593" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1593" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1594" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1594" s="2">
+        <v>46072</v>
+      </c>
+      <c r="C1594" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1594" s="26" t="str">
+        <f t="shared" si="51"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1594">
+        <v>7897</v>
+      </c>
+      <c r="F1594" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1594" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1595" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1595" s="2">
+        <v>46072</v>
+      </c>
+      <c r="C1595" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1595" s="26" t="str">
+        <f t="shared" si="51"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1595">
+        <v>8418</v>
+      </c>
+      <c r="F1595" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1595" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1596" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1596" s="2">
+        <v>46072</v>
+      </c>
+      <c r="C1596" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1596" s="26" t="str">
+        <f t="shared" si="51"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1596">
+        <v>2032</v>
+      </c>
+      <c r="F1596" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1596" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1597" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1597" s="2">
+        <v>46073</v>
+      </c>
+      <c r="C1597" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1597" s="26" t="str">
+        <f t="shared" ref="D1597:D1612" si="52">TEXT(B1597, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="E1597">
+        <v>2390</v>
+      </c>
+      <c r="F1597" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1597" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1598" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1598" s="2">
+        <v>46073</v>
+      </c>
+      <c r="C1598" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1598" s="26" t="str">
+        <f t="shared" si="52"/>
+        <v>Friday</v>
+      </c>
+      <c r="F1598" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1598" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1599" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1599" s="2">
+        <v>46073</v>
+      </c>
+      <c r="C1599" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1599" s="26" t="str">
+        <f t="shared" si="52"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1599">
+        <v>2250</v>
+      </c>
+      <c r="F1599" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1599" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1600" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1600" s="2">
+        <v>46073</v>
+      </c>
+      <c r="C1600" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1600" s="26" t="str">
+        <f t="shared" si="52"/>
+        <v>Friday</v>
+      </c>
+      <c r="F1600" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1600" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1601" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1601" s="2">
+        <v>46073</v>
+      </c>
+      <c r="C1601" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1601" s="26" t="str">
+        <f t="shared" si="52"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1601">
+        <v>1840.6</v>
+      </c>
+      <c r="F1601" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1601" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1602" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1602" s="2">
+        <v>46073</v>
+      </c>
+      <c r="C1602" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1602" s="26" t="str">
+        <f t="shared" si="52"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1602">
+        <v>3677</v>
+      </c>
+      <c r="F1602" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1602" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1603" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1603" s="2">
+        <v>46073</v>
+      </c>
+      <c r="C1603" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1603" s="26" t="str">
+        <f t="shared" si="52"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1603">
+        <v>3257</v>
+      </c>
+      <c r="F1603" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1603" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1604" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1604" s="2">
+        <v>46073</v>
+      </c>
+      <c r="C1604" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1604" s="26" t="str">
+        <f t="shared" si="52"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1604">
+        <v>7672</v>
+      </c>
+      <c r="F1604" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1604" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1605" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1605" s="2">
+        <v>46073</v>
+      </c>
+      <c r="C1605" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1605" s="26" t="str">
+        <f t="shared" si="52"/>
+        <v>Friday</v>
+      </c>
+      <c r="F1605" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1605" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1606" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1606" s="2">
+        <v>46073</v>
+      </c>
+      <c r="C1606" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1606" s="26" t="str">
+        <f t="shared" si="52"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1606">
+        <v>3189</v>
+      </c>
+      <c r="F1606" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1606" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1607" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1607" s="2">
+        <v>46073</v>
+      </c>
+      <c r="C1607" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1607" s="26" t="str">
+        <f t="shared" si="52"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1607">
+        <v>7594</v>
+      </c>
+      <c r="F1607" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1607" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1608" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1608" s="2">
+        <v>46073</v>
+      </c>
+      <c r="C1608" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1608" s="26" t="str">
+        <f t="shared" si="52"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1608">
+        <v>13262</v>
+      </c>
+      <c r="F1608" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1608" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1609" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1609" s="2">
+        <v>46073</v>
+      </c>
+      <c r="C1609" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1609" s="26" t="str">
+        <f t="shared" si="52"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1609">
+        <v>10462</v>
+      </c>
+      <c r="F1609" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1609" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1610" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1610" s="2">
+        <v>46073</v>
+      </c>
+      <c r="C1610" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1610" s="26" t="str">
+        <f t="shared" si="52"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1610">
+        <v>11886</v>
+      </c>
+      <c r="F1610" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1610" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1611" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1611" s="2">
+        <v>46073</v>
+      </c>
+      <c r="C1611" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1611" s="26" t="str">
+        <f t="shared" si="52"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1611">
+        <v>2550</v>
+      </c>
+      <c r="F1611" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1611" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1612" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1612" s="2">
+        <v>46073</v>
+      </c>
+      <c r="C1612" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1612" s="26" t="str">
+        <f t="shared" si="52"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1612">
+        <v>1710</v>
+      </c>
+      <c r="F1612" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1612" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1613" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1613" s="2">
+        <v>46076</v>
+      </c>
+      <c r="C1613" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1613" s="26" t="str">
+        <f t="shared" ref="D1613:D1628" si="53">TEXT(B1613, "dddd")</f>
+        <v>Monday</v>
+      </c>
+      <c r="E1613">
+        <v>3243.4</v>
+      </c>
+      <c r="F1613" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1613" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1614" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1614" s="2">
+        <v>46076</v>
+      </c>
+      <c r="C1614" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1614" s="26" t="str">
+        <f t="shared" si="53"/>
+        <v>Monday</v>
+      </c>
+      <c r="F1614" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1614" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1615" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1615" s="2">
+        <v>46076</v>
+      </c>
+      <c r="C1615" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1615" s="26" t="str">
+        <f t="shared" si="53"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1615">
+        <v>1918</v>
+      </c>
+      <c r="F1615" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1615" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1616" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1616" s="2">
+        <v>46076</v>
+      </c>
+      <c r="C1616" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1616" s="26" t="str">
+        <f t="shared" si="53"/>
+        <v>Monday</v>
+      </c>
+      <c r="F1616" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1616" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1617" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1617" s="2">
+        <v>46076</v>
+      </c>
+      <c r="C1617" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1617" s="26" t="str">
+        <f t="shared" si="53"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1617">
+        <v>2387.8000000000002</v>
+      </c>
+      <c r="F1617" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1617" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1618" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1618" s="2">
+        <v>46076</v>
+      </c>
+      <c r="C1618" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1618" s="26" t="str">
+        <f t="shared" si="53"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1618">
+        <v>4486</v>
+      </c>
+      <c r="F1618" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1618" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1619" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1619" s="2">
+        <v>46076</v>
+      </c>
+      <c r="C1619" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1619" s="26" t="str">
+        <f t="shared" si="53"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1619">
+        <v>680</v>
+      </c>
+      <c r="F1619" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1619" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1620" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1620" s="2">
+        <v>46076</v>
+      </c>
+      <c r="C1620" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1620" s="26" t="str">
+        <f t="shared" si="53"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1620">
+        <v>11260</v>
+      </c>
+      <c r="F1620" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1620" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1621" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1621" s="2">
+        <v>46076</v>
+      </c>
+      <c r="C1621" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1621" s="26" t="str">
+        <f t="shared" si="53"/>
+        <v>Monday</v>
+      </c>
+      <c r="F1621" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1621" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1622" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1622" s="2">
+        <v>46076</v>
+      </c>
+      <c r="C1622" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1622" s="26" t="str">
+        <f t="shared" si="53"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1622">
+        <v>4342</v>
+      </c>
+      <c r="F1622" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1622" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1623" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1623" s="2">
+        <v>46076</v>
+      </c>
+      <c r="C1623" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1623" s="26" t="str">
+        <f t="shared" si="53"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1623">
+        <v>8287</v>
+      </c>
+      <c r="F1623" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1623" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1624" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1624" s="2">
+        <v>46076</v>
+      </c>
+      <c r="C1624" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1624" s="26" t="str">
+        <f t="shared" si="53"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1624">
+        <v>12336</v>
+      </c>
+      <c r="F1624" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1624" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1625" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1625" s="2">
+        <v>46076</v>
+      </c>
+      <c r="C1625" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1625" s="26" t="str">
+        <f t="shared" si="53"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1625">
+        <v>16594</v>
+      </c>
+      <c r="F1625" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1625" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1626" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1626" s="2">
+        <v>46076</v>
+      </c>
+      <c r="C1626" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1626" s="26" t="str">
+        <f t="shared" si="53"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1626">
+        <v>7128</v>
+      </c>
+      <c r="F1626" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1626" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1627" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1627" s="2">
+        <v>46076</v>
+      </c>
+      <c r="C1627" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1627" s="26" t="str">
+        <f t="shared" si="53"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1627">
+        <v>8824</v>
+      </c>
+      <c r="F1627" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1627" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1628" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1628" s="2">
+        <v>46076</v>
+      </c>
+      <c r="C1628" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1628" s="26" t="str">
+        <f t="shared" si="53"/>
+        <v>Monday</v>
+      </c>
+      <c r="E1628">
+        <v>2499</v>
+      </c>
+      <c r="F1628" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1628" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1629" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1629" s="2">
+        <v>46077</v>
+      </c>
+      <c r="C1629" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1629" s="26" t="str">
+        <f t="shared" ref="D1629:D1644" si="54">TEXT(B1629, "dddd")</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1629">
+        <v>3685</v>
+      </c>
+      <c r="F1629" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1629" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1630" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1630" s="2">
+        <v>46077</v>
+      </c>
+      <c r="C1630" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1630" s="26" t="str">
+        <f t="shared" si="54"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1630">
+        <v>5047</v>
+      </c>
+      <c r="F1630" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1630" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1631" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1631" s="2">
+        <v>46077</v>
+      </c>
+      <c r="C1631" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1631" s="26" t="str">
+        <f t="shared" si="54"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1631">
+        <v>3584</v>
+      </c>
+      <c r="F1631" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1631" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1632" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1632" s="2">
+        <v>46077</v>
+      </c>
+      <c r="C1632" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1632" s="26" t="str">
+        <f t="shared" si="54"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="F1632" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1632" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1633" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1633" s="2">
+        <v>46077</v>
+      </c>
+      <c r="C1633" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1633" s="26" t="str">
+        <f t="shared" si="54"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1633">
+        <v>3031.6</v>
+      </c>
+      <c r="F1633" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1633" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1634" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1634" s="2">
+        <v>46077</v>
+      </c>
+      <c r="C1634" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1634" s="26" t="str">
+        <f t="shared" si="54"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1634">
+        <v>2066</v>
+      </c>
+      <c r="F1634" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1634" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1635" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1635" s="2">
+        <v>46077</v>
+      </c>
+      <c r="C1635" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1635" s="26" t="str">
+        <f t="shared" si="54"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="F1635" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1635" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1636" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1636" s="2">
+        <v>46077</v>
+      </c>
+      <c r="C1636" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1636" s="26" t="str">
+        <f t="shared" si="54"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1636">
+        <v>7700</v>
+      </c>
+      <c r="F1636" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1636" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1637" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1637" s="2">
+        <v>46077</v>
+      </c>
+      <c r="C1637" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1637" s="26" t="str">
+        <f t="shared" si="54"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="F1637" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1637" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1638" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1638" s="2">
+        <v>46077</v>
+      </c>
+      <c r="C1638" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1638" s="26" t="str">
+        <f t="shared" si="54"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1638">
+        <v>6973</v>
+      </c>
+      <c r="F1638" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1638" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1639" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1639" s="2">
+        <v>46077</v>
+      </c>
+      <c r="C1639" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1639" s="26" t="str">
+        <f t="shared" si="54"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1639">
+        <v>5030</v>
+      </c>
+      <c r="F1639" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1639" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1640" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1640" s="2">
+        <v>46077</v>
+      </c>
+      <c r="C1640" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1640" s="26" t="str">
+        <f t="shared" si="54"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1640">
+        <v>11127</v>
+      </c>
+      <c r="F1640" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1640" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1641" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1641" s="2">
+        <v>46077</v>
+      </c>
+      <c r="C1641" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1641" s="26" t="str">
+        <f t="shared" si="54"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1641">
+        <v>15828</v>
+      </c>
+      <c r="F1641" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1641" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1642" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1642" s="2">
+        <v>46077</v>
+      </c>
+      <c r="C1642" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1642" s="26" t="str">
+        <f t="shared" si="54"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1642">
+        <v>11267</v>
+      </c>
+      <c r="F1642" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1642" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1643" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1643" s="2">
+        <v>46077</v>
+      </c>
+      <c r="C1643" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1643" s="26" t="str">
+        <f t="shared" si="54"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1643">
+        <v>7811</v>
+      </c>
+      <c r="F1643" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1643" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1644" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1644" s="2">
+        <v>46077</v>
+      </c>
+      <c r="C1644" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1644" s="26" t="str">
+        <f t="shared" si="54"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="E1644">
+        <v>1478</v>
+      </c>
+      <c r="F1644" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1644" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1645" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1645" s="2">
+        <v>46078</v>
+      </c>
+      <c r="C1645" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1645" s="26" t="str">
+        <f t="shared" ref="D1645:D1660" si="55">TEXT(B1645, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1645">
+        <v>3947</v>
+      </c>
+      <c r="F1645" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1645" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1646" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1646" s="2">
+        <v>46078</v>
+      </c>
+      <c r="C1646" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1646" s="26" t="str">
+        <f t="shared" si="55"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1646">
+        <v>5638</v>
+      </c>
+      <c r="F1646" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1646" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1647" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1647" s="2">
+        <v>46078</v>
+      </c>
+      <c r="C1647" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1647" s="26" t="str">
+        <f t="shared" si="55"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1647">
+        <v>8576</v>
+      </c>
+      <c r="F1647" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1647" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1648" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1648" s="2">
+        <v>46078</v>
+      </c>
+      <c r="C1648" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1648" s="26" t="str">
+        <f t="shared" si="55"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1648">
+        <v>120</v>
+      </c>
+      <c r="F1648" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1648" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1649" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1649" s="2">
+        <v>46078</v>
+      </c>
+      <c r="C1649" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1649" s="26" t="str">
+        <f t="shared" si="55"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1649">
+        <v>1410</v>
+      </c>
+      <c r="F1649" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1649" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1650" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1650" s="2">
+        <v>46078</v>
+      </c>
+      <c r="C1650" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1650" s="26" t="str">
+        <f t="shared" si="55"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1650">
+        <v>1515</v>
+      </c>
+      <c r="F1650" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1650" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1651" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1651" s="2">
+        <v>46078</v>
+      </c>
+      <c r="C1651" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1651" s="26" t="str">
+        <f t="shared" si="55"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1651">
+        <v>1219</v>
+      </c>
+      <c r="F1651" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1651" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1652" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1652" s="2">
+        <v>46078</v>
+      </c>
+      <c r="C1652" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1652" s="26" t="str">
+        <f t="shared" si="55"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1652">
+        <v>11632</v>
+      </c>
+      <c r="F1652" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1652" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1653" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1653" s="2">
+        <v>46078</v>
+      </c>
+      <c r="C1653" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1653" s="26" t="str">
+        <f t="shared" si="55"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="F1653" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1653" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1654" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1654" s="2">
+        <v>46078</v>
+      </c>
+      <c r="C1654" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1654" s="26" t="str">
+        <f t="shared" si="55"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1654">
+        <v>6304</v>
+      </c>
+      <c r="F1654" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1654" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1655" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1655" s="2">
+        <v>46078</v>
+      </c>
+      <c r="C1655" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1655" s="26" t="str">
+        <f t="shared" si="55"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1655">
+        <v>10115</v>
+      </c>
+      <c r="F1655" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1655" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1656" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1656" s="2">
+        <v>46078</v>
+      </c>
+      <c r="C1656" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1656" s="26" t="str">
+        <f t="shared" si="55"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1656">
+        <v>7481</v>
+      </c>
+      <c r="F1656" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1656" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1657" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1657" s="2">
+        <v>46078</v>
+      </c>
+      <c r="C1657" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1657" s="26" t="str">
+        <f t="shared" si="55"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1657">
+        <v>18495</v>
+      </c>
+      <c r="F1657" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1657" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1658" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1658" s="2">
+        <v>46078</v>
+      </c>
+      <c r="C1658" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1658" s="26" t="str">
+        <f t="shared" si="55"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1658">
+        <v>6887</v>
+      </c>
+      <c r="F1658" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1658" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1659" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1659" s="2">
+        <v>46078</v>
+      </c>
+      <c r="C1659" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1659" s="26" t="str">
+        <f t="shared" si="55"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="E1659">
+        <v>4760</v>
+      </c>
+      <c r="F1659" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1659" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1660" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1660" s="2">
+        <v>46078</v>
+      </c>
+      <c r="C1660" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1660" s="26" t="str">
+        <f t="shared" si="55"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="F1660" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1660" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1661" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1661" s="2">
+        <v>46079</v>
+      </c>
+      <c r="C1661" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1661" s="26" t="str">
+        <f t="shared" ref="D1661:D1676" si="56">TEXT(B1661, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E1661">
+        <v>2787</v>
+      </c>
+      <c r="F1661" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1661" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1662" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1662" s="2">
+        <v>46079</v>
+      </c>
+      <c r="C1662" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1662" s="26" t="str">
+        <f t="shared" si="56"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1662">
+        <v>6198</v>
+      </c>
+      <c r="F1662" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1662" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1663" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1663" s="2">
+        <v>46079</v>
+      </c>
+      <c r="C1663" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1663" s="26" t="str">
+        <f t="shared" si="56"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1663">
+        <v>4730</v>
+      </c>
+      <c r="F1663" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1663" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1664" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1664" s="2">
+        <v>46079</v>
+      </c>
+      <c r="C1664" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1664" s="26" t="str">
+        <f t="shared" si="56"/>
+        <v>Thursday</v>
+      </c>
+      <c r="F1664" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1664" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1665" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1665" s="2">
+        <v>46079</v>
+      </c>
+      <c r="C1665" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1665" s="26" t="str">
+        <f t="shared" si="56"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1665">
+        <v>1776</v>
+      </c>
+      <c r="F1665" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1665" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1666" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1666" s="2">
+        <v>46079</v>
+      </c>
+      <c r="C1666" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1666" s="26" t="str">
+        <f t="shared" si="56"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1666">
+        <v>2297</v>
+      </c>
+      <c r="F1666" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1666" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1667" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1667" s="2">
+        <v>46079</v>
+      </c>
+      <c r="C1667" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1667" s="26" t="str">
+        <f t="shared" si="56"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1667">
+        <v>8703</v>
+      </c>
+      <c r="F1667" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1667" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1668" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1668" s="2">
+        <v>46079</v>
+      </c>
+      <c r="C1668" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1668" s="26" t="str">
+        <f t="shared" si="56"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1668">
+        <v>4784</v>
+      </c>
+      <c r="F1668" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1668" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1669" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1669" s="2">
+        <v>46079</v>
+      </c>
+      <c r="C1669" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1669" s="26" t="str">
+        <f t="shared" si="56"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1669">
+        <v>1397</v>
+      </c>
+      <c r="F1669" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1669" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1670" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1670" s="2">
+        <v>46079</v>
+      </c>
+      <c r="C1670" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1670" s="26" t="str">
+        <f t="shared" si="56"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1670">
+        <v>5292</v>
+      </c>
+      <c r="F1670" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1670" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1671" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1671" s="2">
+        <v>46079</v>
+      </c>
+      <c r="C1671" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1671" s="26" t="str">
+        <f t="shared" si="56"/>
+        <v>Thursday</v>
+      </c>
+      <c r="F1671" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1671" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1672" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1672" s="2">
+        <v>46079</v>
+      </c>
+      <c r="C1672" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1672" s="26" t="str">
+        <f t="shared" si="56"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1672">
+        <v>12053</v>
+      </c>
+      <c r="F1672" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1672" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1673" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1673" s="2">
+        <v>46079</v>
+      </c>
+      <c r="C1673" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1673" s="26" t="str">
+        <f t="shared" si="56"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1673">
+        <v>18934</v>
+      </c>
+      <c r="F1673" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1673" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1674" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1674" s="2">
+        <v>46079</v>
+      </c>
+      <c r="C1674" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1674" s="26" t="str">
+        <f t="shared" si="56"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1674">
+        <v>10271</v>
+      </c>
+      <c r="F1674" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1674" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1675" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1675" s="2">
+        <v>46079</v>
+      </c>
+      <c r="C1675" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1675" s="26" t="str">
+        <f t="shared" si="56"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1675">
+        <v>6365</v>
+      </c>
+      <c r="F1675" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1675" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1676" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1676" s="2">
+        <v>46079</v>
+      </c>
+      <c r="C1676" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1676" s="26" t="str">
+        <f t="shared" si="56"/>
+        <v>Thursday</v>
+      </c>
+      <c r="E1676">
+        <v>1900</v>
+      </c>
+      <c r="F1676" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1676" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1677" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1677" s="2">
+        <v>46080</v>
+      </c>
+      <c r="C1677" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1677" s="26" t="str">
+        <f t="shared" ref="D1677:D1692" si="57">TEXT(B1677, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="E1677">
+        <v>3264.4</v>
+      </c>
+      <c r="F1677" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1677" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1678" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1678" s="2">
+        <v>46080</v>
+      </c>
+      <c r="C1678" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1678" s="26" t="str">
+        <f t="shared" si="57"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1678">
+        <v>10260</v>
+      </c>
+      <c r="F1678" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1678" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1679" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1679" s="2">
+        <v>46080</v>
+      </c>
+      <c r="C1679" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1679" s="26" t="str">
+        <f t="shared" si="57"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1679">
+        <v>8292</v>
+      </c>
+      <c r="F1679" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1679" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1680" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1680" s="2">
+        <v>46080</v>
+      </c>
+      <c r="C1680" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1680" s="26" t="str">
+        <f t="shared" si="57"/>
+        <v>Friday</v>
+      </c>
+      <c r="F1680" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1680" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1681" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1681" s="2">
+        <v>46080</v>
+      </c>
+      <c r="C1681" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1681" s="26" t="str">
+        <f t="shared" si="57"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1681">
+        <v>1995</v>
+      </c>
+      <c r="F1681" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1681" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1682" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1682" s="2">
+        <v>46080</v>
+      </c>
+      <c r="C1682" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1682" s="26" t="str">
+        <f t="shared" si="57"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1682">
+        <v>4336</v>
+      </c>
+      <c r="F1682" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1682" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1683" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1683" s="2">
+        <v>46080</v>
+      </c>
+      <c r="C1683" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1683" s="26" t="str">
+        <f t="shared" si="57"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1683">
+        <v>6948</v>
+      </c>
+      <c r="F1683" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1683" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1684" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1684" s="2">
+        <v>46080</v>
+      </c>
+      <c r="C1684" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1684" s="26" t="str">
+        <f t="shared" si="57"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1684">
+        <v>10764</v>
+      </c>
+      <c r="F1684" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1684" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1685" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1685" s="2">
+        <v>46080</v>
+      </c>
+      <c r="C1685" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1685" s="26" t="str">
+        <f t="shared" si="57"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1685">
+        <v>2255</v>
+      </c>
+      <c r="F1685" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1685" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1686" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1686" s="2">
+        <v>46080</v>
+      </c>
+      <c r="C1686" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1686" s="26" t="str">
+        <f t="shared" si="57"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1686">
+        <v>3040.5</v>
+      </c>
+      <c r="F1686" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1686" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1687" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1687" s="2">
+        <v>46080</v>
+      </c>
+      <c r="C1687" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1687" s="26" t="str">
+        <f t="shared" si="57"/>
+        <v>Friday</v>
+      </c>
+      <c r="F1687" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1687" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1688" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1688" s="2">
+        <v>46080</v>
+      </c>
+      <c r="C1688" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1688" s="26" t="str">
+        <f t="shared" si="57"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1688">
+        <v>11418</v>
+      </c>
+      <c r="F1688" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1688" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1689" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1689" s="2">
+        <v>46080</v>
+      </c>
+      <c r="C1689" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1689" s="26" t="str">
+        <f t="shared" si="57"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1689">
+        <v>19778</v>
+      </c>
+      <c r="F1689" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1689" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1690" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1690" s="2">
+        <v>46080</v>
+      </c>
+      <c r="C1690" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1690" s="26" t="str">
+        <f t="shared" si="57"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1690">
+        <v>14832</v>
+      </c>
+      <c r="F1690" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1690" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1691" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1691" s="2">
+        <v>46080</v>
+      </c>
+      <c r="C1691" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1691" s="26" t="str">
+        <f t="shared" si="57"/>
+        <v>Friday</v>
+      </c>
+      <c r="E1691">
+        <v>9195</v>
+      </c>
+      <c r="F1691" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1691" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1692" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1692" s="2">
+        <v>46080</v>
+      </c>
+      <c r="C1692" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1692" s="26" t="str">
+        <f t="shared" si="57"/>
+        <v>Friday</v>
+      </c>
+      <c r="F1692" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1692" s="26" t="s">
         <v>40</v>
       </c>
     </row>

--- a/data_inputs/daily_logs.xlsx
+++ b/data_inputs/daily_logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://komaralliance-my.sharepoint.com/personal/dshao_komar_com/Documents/Production Logs/data_inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2325" documentId="8_{EA7A99F6-1694-487A-9FFB-F46B9189E3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B10F752A-8F50-4410-AF4E-C6D6947505A0}"/>
+  <xr:revisionPtr revIDLastSave="2528" documentId="8_{EA7A99F6-1694-487A-9FFB-F46B9189E3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8079E247-7FFE-4E02-9C18-D0B8BD4225CF}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-12660" windowWidth="16440" windowHeight="28320" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="13" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8600" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9124" uniqueCount="64">
   <si>
     <t>Production Output</t>
   </si>
@@ -307,7 +307,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -349,11 +349,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3251,156 +3252,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000001000000}" name="PivotTable5" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Machine">
-  <location ref="A5:E18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="7">
-    <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending">
-      <items count="13">
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="13">
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-    <i i="3">
-      <x v="3"/>
-    </i>
-  </colItems>
-  <dataFields count="4">
-    <dataField name="Avg Daily LB Produced" fld="4" subtotal="average" baseField="3" baseItem="0" numFmtId="1"/>
-    <dataField name="# Shifts" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Most Productive Day" fld="4" subtotal="max" baseField="0" baseItem="5"/>
-    <dataField name="Least Productive Day" fld="4" subtotal="min" baseField="0" baseItem="5"/>
-  </dataFields>
-  <formats count="5">
-    <format dxfId="9">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="8">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="7">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="2"/>
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="6">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="5">
-      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable2" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Shift/ Machine">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Shift/ Machine">
   <location ref="A21:E46" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending">
@@ -3547,6 +3399,155 @@
     <dataField name="Least Productive Day" fld="4" subtotal="min" baseField="0" baseItem="5"/>
   </dataFields>
   <formats count="5">
+    <format dxfId="9">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="8">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="7">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="2"/>
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="6">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="5">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000001000000}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Machine">
+  <location ref="A5:E18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending">
+      <items count="13">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
+  </colItems>
+  <dataFields count="4">
+    <dataField name="Avg Daily LB Produced" fld="4" subtotal="average" baseField="3" baseItem="0" numFmtId="1"/>
+    <dataField name="# Shifts" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Most Productive Day" fld="4" subtotal="max" baseField="0" baseItem="5"/>
+    <dataField name="Least Productive Day" fld="4" subtotal="min" baseField="0" baseItem="5"/>
+  </dataFields>
+  <formats count="5">
     <format dxfId="14">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
@@ -3573,7 +3574,7 @@
       </pivotArea>
     </format>
     <format dxfId="10">
-      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -3946,12 +3947,12 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
     </row>
     <row r="5" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
@@ -4202,12 +4203,12 @@
       <c r="E19" s="3"/>
     </row>
     <row r="20" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
     </row>
     <row r="21" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
@@ -7187,7 +7188,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G2093"/>
+  <dimension ref="A1:G2224"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
@@ -14365,7 +14366,7 @@
       <c r="A309" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B309" s="29">
+      <c r="B309" s="28">
         <v>45926</v>
       </c>
       <c r="C309" t="s">
@@ -14389,7 +14390,7 @@
       <c r="A310" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B310" s="29">
+      <c r="B310" s="28">
         <v>45926</v>
       </c>
       <c r="C310" t="s">
@@ -14413,7 +14414,7 @@
       <c r="A311" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="B311" s="29">
+      <c r="B311" s="28">
         <v>45926</v>
       </c>
       <c r="C311" t="s">
@@ -14437,7 +14438,7 @@
       <c r="A312" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B312" s="29">
+      <c r="B312" s="28">
         <v>45926</v>
       </c>
       <c r="C312" t="s">
@@ -14458,7 +14459,7 @@
       <c r="A313" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B313" s="29">
+      <c r="B313" s="28">
         <v>45926</v>
       </c>
       <c r="C313" t="s">
@@ -14482,7 +14483,7 @@
       <c r="A314" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B314" s="29">
+      <c r="B314" s="28">
         <v>45926</v>
       </c>
       <c r="C314" t="s">
@@ -14506,7 +14507,7 @@
       <c r="A315" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="B315" s="29">
+      <c r="B315" s="28">
         <v>45926</v>
       </c>
       <c r="C315" t="s">
@@ -14530,7 +14531,7 @@
       <c r="A316" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="B316" s="29">
+      <c r="B316" s="28">
         <v>45926</v>
       </c>
       <c r="C316" t="s">
@@ -14554,7 +14555,7 @@
       <c r="A317" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="B317" s="29">
+      <c r="B317" s="28">
         <v>45926</v>
       </c>
       <c r="C317" t="s">
@@ -14578,7 +14579,7 @@
       <c r="A318" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B318" s="29">
+      <c r="B318" s="28">
         <v>45926</v>
       </c>
       <c r="C318" t="s">
@@ -14602,7 +14603,7 @@
       <c r="A319" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B319" s="29">
+      <c r="B319" s="28">
         <v>45926</v>
       </c>
       <c r="C319" t="s">
@@ -14626,7 +14627,7 @@
       <c r="A320" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B320" s="29">
+      <c r="B320" s="28">
         <v>45926</v>
       </c>
       <c r="C320" t="s">
@@ -14650,7 +14651,7 @@
       <c r="A321" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B321" s="29">
+      <c r="B321" s="28">
         <v>45926</v>
       </c>
       <c r="C321" t="s">
@@ -14674,7 +14675,7 @@
       <c r="A322" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="B322" s="29">
+      <c r="B322" s="28">
         <v>45926</v>
       </c>
       <c r="C322" t="s">
@@ -14695,7 +14696,7 @@
       <c r="A323" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B323" s="29">
+      <c r="B323" s="28">
         <v>45926</v>
       </c>
       <c r="C323" t="s">
@@ -14719,7 +14720,7 @@
       <c r="A324" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B324" s="29">
+      <c r="B324" s="28">
         <v>45926</v>
       </c>
       <c r="C324" t="s">
@@ -14743,7 +14744,7 @@
       <c r="A325" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="B325" s="29">
+      <c r="B325" s="28">
         <v>45926</v>
       </c>
       <c r="C325" t="s">
@@ -14764,7 +14765,7 @@
       <c r="A326" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="B326" s="29">
+      <c r="B326" s="28">
         <v>45926</v>
       </c>
       <c r="C326" t="s">
@@ -14785,7 +14786,7 @@
       <c r="A327" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="B327" s="29">
+      <c r="B327" s="28">
         <v>45926</v>
       </c>
       <c r="C327" t="s">
@@ -14806,7 +14807,7 @@
       <c r="A328" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B328" s="29">
+      <c r="B328" s="28">
         <v>45926</v>
       </c>
       <c r="C328" t="s">
@@ -14827,7 +14828,7 @@
       <c r="A329" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B329" s="29">
+      <c r="B329" s="28">
         <v>45926</v>
       </c>
       <c r="C329" t="s">
@@ -14851,7 +14852,7 @@
       <c r="A330" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B330" s="29">
+      <c r="B330" s="28">
         <v>45929</v>
       </c>
       <c r="C330" t="s">
@@ -14875,7 +14876,7 @@
       <c r="A331" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B331" s="29">
+      <c r="B331" s="28">
         <v>45929</v>
       </c>
       <c r="C331" t="s">
@@ -14899,7 +14900,7 @@
       <c r="A332" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="B332" s="29">
+      <c r="B332" s="28">
         <v>45929</v>
       </c>
       <c r="C332" t="s">
@@ -14923,7 +14924,7 @@
       <c r="A333" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B333" s="29">
+      <c r="B333" s="28">
         <v>45929</v>
       </c>
       <c r="C333" t="s">
@@ -14947,7 +14948,7 @@
       <c r="A334" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B334" s="29">
+      <c r="B334" s="28">
         <v>45929</v>
       </c>
       <c r="C334" t="s">
@@ -14971,7 +14972,7 @@
       <c r="A335" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B335" s="29">
+      <c r="B335" s="28">
         <v>45929</v>
       </c>
       <c r="C335" t="s">
@@ -14995,7 +14996,7 @@
       <c r="A336" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="B336" s="29">
+      <c r="B336" s="28">
         <v>45929</v>
       </c>
       <c r="C336" t="s">
@@ -15019,7 +15020,7 @@
       <c r="A337" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="B337" s="29">
+      <c r="B337" s="28">
         <v>45929</v>
       </c>
       <c r="C337" t="s">
@@ -15043,7 +15044,7 @@
       <c r="A338" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="B338" s="29">
+      <c r="B338" s="28">
         <v>45929</v>
       </c>
       <c r="C338" t="s">
@@ -15067,7 +15068,7 @@
       <c r="A339" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B339" s="29">
+      <c r="B339" s="28">
         <v>45929</v>
       </c>
       <c r="C339" t="s">
@@ -15091,7 +15092,7 @@
       <c r="A340" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B340" s="29">
+      <c r="B340" s="28">
         <v>45929</v>
       </c>
       <c r="C340" t="s">
@@ -15115,7 +15116,7 @@
       <c r="A341" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B341" s="29">
+      <c r="B341" s="28">
         <v>45929</v>
       </c>
       <c r="C341" t="s">
@@ -15139,7 +15140,7 @@
       <c r="A342" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B342" s="29">
+      <c r="B342" s="28">
         <v>45929</v>
       </c>
       <c r="C342" t="s">
@@ -15163,7 +15164,7 @@
       <c r="A343" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="B343" s="29">
+      <c r="B343" s="28">
         <v>45929</v>
       </c>
       <c r="C343" t="s">
@@ -15184,7 +15185,7 @@
       <c r="A344" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B344" s="29">
+      <c r="B344" s="28">
         <v>45929</v>
       </c>
       <c r="C344" t="s">
@@ -15208,7 +15209,7 @@
       <c r="A345" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B345" s="29">
+      <c r="B345" s="28">
         <v>45929</v>
       </c>
       <c r="C345" t="s">
@@ -15232,7 +15233,7 @@
       <c r="A346" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="B346" s="29">
+      <c r="B346" s="28">
         <v>45929</v>
       </c>
       <c r="C346" t="s">
@@ -15253,7 +15254,7 @@
       <c r="A347" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="B347" s="29">
+      <c r="B347" s="28">
         <v>45929</v>
       </c>
       <c r="C347" t="s">
@@ -15277,7 +15278,7 @@
       <c r="A348" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="B348" s="29">
+      <c r="B348" s="28">
         <v>45929</v>
       </c>
       <c r="C348" t="s">
@@ -15298,7 +15299,7 @@
       <c r="A349" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B349" s="29">
+      <c r="B349" s="28">
         <v>45929</v>
       </c>
       <c r="C349" t="s">
@@ -15319,7 +15320,7 @@
       <c r="A350" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B350" s="29">
+      <c r="B350" s="28">
         <v>45929</v>
       </c>
       <c r="C350" t="s">
@@ -15343,7 +15344,7 @@
       <c r="A351" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B351" s="29">
+      <c r="B351" s="28">
         <v>45930</v>
       </c>
       <c r="C351" t="s">
@@ -15367,7 +15368,7 @@
       <c r="A352" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B352" s="29">
+      <c r="B352" s="28">
         <v>45930</v>
       </c>
       <c r="C352" t="s">
@@ -15391,7 +15392,7 @@
       <c r="A353" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="B353" s="29">
+      <c r="B353" s="28">
         <v>45930</v>
       </c>
       <c r="C353" t="s">
@@ -15415,7 +15416,7 @@
       <c r="A354" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B354" s="29">
+      <c r="B354" s="28">
         <v>45930</v>
       </c>
       <c r="C354" t="s">
@@ -15439,7 +15440,7 @@
       <c r="A355" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B355" s="29">
+      <c r="B355" s="28">
         <v>45930</v>
       </c>
       <c r="C355" t="s">
@@ -15463,7 +15464,7 @@
       <c r="A356" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="B356" s="29">
+      <c r="B356" s="28">
         <v>45930</v>
       </c>
       <c r="C356" t="s">
@@ -15487,7 +15488,7 @@
       <c r="A357" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="B357" s="29">
+      <c r="B357" s="28">
         <v>45930</v>
       </c>
       <c r="C357" t="s">
@@ -15511,7 +15512,7 @@
       <c r="A358" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="B358" s="29">
+      <c r="B358" s="28">
         <v>45930</v>
       </c>
       <c r="C358" t="s">
@@ -15535,7 +15536,7 @@
       <c r="A359" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B359" s="29">
+      <c r="B359" s="28">
         <v>45930</v>
       </c>
       <c r="C359" t="s">
@@ -15559,7 +15560,7 @@
       <c r="A360" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B360" s="29">
+      <c r="B360" s="28">
         <v>45930</v>
       </c>
       <c r="C360" t="s">
@@ -15583,7 +15584,7 @@
       <c r="A361" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B361" s="29">
+      <c r="B361" s="28">
         <v>45930</v>
       </c>
       <c r="C361" t="s">
@@ -15607,7 +15608,7 @@
       <c r="A362" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B362" s="29">
+      <c r="B362" s="28">
         <v>45930</v>
       </c>
       <c r="C362" t="s">
@@ -15631,7 +15632,7 @@
       <c r="A363" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="B363" s="29">
+      <c r="B363" s="28">
         <v>45930</v>
       </c>
       <c r="C363" t="s">
@@ -15652,7 +15653,7 @@
       <c r="A364" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B364" s="29">
+      <c r="B364" s="28">
         <v>45930</v>
       </c>
       <c r="C364" t="s">
@@ -15676,7 +15677,7 @@
       <c r="A365" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B365" s="29">
+      <c r="B365" s="28">
         <v>45930</v>
       </c>
       <c r="C365" t="s">
@@ -15700,7 +15701,7 @@
       <c r="A366" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="B366" s="29">
+      <c r="B366" s="28">
         <v>45930</v>
       </c>
       <c r="C366" t="s">
@@ -15721,7 +15722,7 @@
       <c r="A367" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="B367" s="29">
+      <c r="B367" s="28">
         <v>45930</v>
       </c>
       <c r="C367" t="s">
@@ -15745,7 +15746,7 @@
       <c r="A368" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="B368" s="29">
+      <c r="B368" s="28">
         <v>45930</v>
       </c>
       <c r="C368" t="s">
@@ -15766,7 +15767,7 @@
       <c r="A369" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B369" s="29">
+      <c r="B369" s="28">
         <v>45930</v>
       </c>
       <c r="C369" t="s">
@@ -15787,7 +15788,7 @@
       <c r="A370" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B370" s="29">
+      <c r="B370" s="28">
         <v>45930</v>
       </c>
       <c r="C370" t="s">
@@ -15808,7 +15809,7 @@
       <c r="A371" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B371" s="29">
+      <c r="B371" s="28">
         <v>45931</v>
       </c>
       <c r="C371" t="s">
@@ -15832,7 +15833,7 @@
       <c r="A372" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B372" s="29">
+      <c r="B372" s="28">
         <v>45931</v>
       </c>
       <c r="C372" t="s">
@@ -15856,7 +15857,7 @@
       <c r="A373" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="B373" s="29">
+      <c r="B373" s="28">
         <v>45931</v>
       </c>
       <c r="C373" t="s">
@@ -15880,7 +15881,7 @@
       <c r="A374" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B374" s="29">
+      <c r="B374" s="28">
         <v>45931</v>
       </c>
       <c r="C374" t="s">
@@ -15901,7 +15902,7 @@
       <c r="A375" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B375" s="29">
+      <c r="B375" s="28">
         <v>45931</v>
       </c>
       <c r="C375" t="s">
@@ -15925,7 +15926,7 @@
       <c r="A376" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B376" s="29">
+      <c r="B376" s="28">
         <v>45931</v>
       </c>
       <c r="C376" t="s">
@@ -15949,7 +15950,7 @@
       <c r="A377" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="B377" s="29">
+      <c r="B377" s="28">
         <v>45931</v>
       </c>
       <c r="C377" t="s">
@@ -15973,7 +15974,7 @@
       <c r="A378" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="B378" s="29">
+      <c r="B378" s="28">
         <v>45931</v>
       </c>
       <c r="C378" t="s">
@@ -15997,7 +15998,7 @@
       <c r="A379" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="B379" s="29">
+      <c r="B379" s="28">
         <v>45931</v>
       </c>
       <c r="C379" t="s">
@@ -16021,7 +16022,7 @@
       <c r="A380" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B380" s="29">
+      <c r="B380" s="28">
         <v>45931</v>
       </c>
       <c r="C380" t="s">
@@ -16045,7 +16046,7 @@
       <c r="A381" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B381" s="29">
+      <c r="B381" s="28">
         <v>45931</v>
       </c>
       <c r="C381" t="s">
@@ -16066,7 +16067,7 @@
       <c r="A382" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B382" s="29">
+      <c r="B382" s="28">
         <v>45931</v>
       </c>
       <c r="C382" t="s">
@@ -16090,7 +16091,7 @@
       <c r="A383" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B383" s="29">
+      <c r="B383" s="28">
         <v>45931</v>
       </c>
       <c r="C383" t="s">
@@ -16111,7 +16112,7 @@
       <c r="A384" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="B384" s="29">
+      <c r="B384" s="28">
         <v>45931</v>
       </c>
       <c r="C384" t="s">
@@ -16132,7 +16133,7 @@
       <c r="A385" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B385" s="29">
+      <c r="B385" s="28">
         <v>45931</v>
       </c>
       <c r="C385" t="s">
@@ -16156,7 +16157,7 @@
       <c r="A386" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B386" s="29">
+      <c r="B386" s="28">
         <v>45931</v>
       </c>
       <c r="C386" t="s">
@@ -16180,7 +16181,7 @@
       <c r="A387" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="B387" s="29">
+      <c r="B387" s="28">
         <v>45931</v>
       </c>
       <c r="C387" t="s">
@@ -16201,7 +16202,7 @@
       <c r="A388" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="B388" s="29">
+      <c r="B388" s="28">
         <v>45931</v>
       </c>
       <c r="C388" t="s">
@@ -16225,7 +16226,7 @@
       <c r="A389" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="B389" s="29">
+      <c r="B389" s="28">
         <v>45931</v>
       </c>
       <c r="C389" t="s">
@@ -16246,7 +16247,7 @@
       <c r="A390" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B390" s="29">
+      <c r="B390" s="28">
         <v>45931</v>
       </c>
       <c r="C390" t="s">
@@ -16267,7 +16268,7 @@
       <c r="A391" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B391" s="29">
+      <c r="B391" s="28">
         <v>45931</v>
       </c>
       <c r="C391" t="s">
@@ -16288,7 +16289,7 @@
       <c r="A392" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B392" s="29">
+      <c r="B392" s="28">
         <v>45932</v>
       </c>
       <c r="C392" t="s">
@@ -16312,7 +16313,7 @@
       <c r="A393" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B393" s="29">
+      <c r="B393" s="28">
         <v>45932</v>
       </c>
       <c r="C393" t="s">
@@ -16333,7 +16334,7 @@
       <c r="A394" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="B394" s="29">
+      <c r="B394" s="28">
         <v>45932</v>
       </c>
       <c r="C394" t="s">
@@ -16357,7 +16358,7 @@
       <c r="A395" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B395" s="29">
+      <c r="B395" s="28">
         <v>45932</v>
       </c>
       <c r="C395" t="s">
@@ -16381,7 +16382,7 @@
       <c r="A396" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B396" s="29">
+      <c r="B396" s="28">
         <v>45932</v>
       </c>
       <c r="C396" t="s">
@@ -16405,7 +16406,7 @@
       <c r="A397" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B397" s="29">
+      <c r="B397" s="28">
         <v>45932</v>
       </c>
       <c r="C397" t="s">
@@ -16426,7 +16427,7 @@
       <c r="A398" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="B398" s="29">
+      <c r="B398" s="28">
         <v>45932</v>
       </c>
       <c r="C398" t="s">
@@ -16450,7 +16451,7 @@
       <c r="A399" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="B399" s="29">
+      <c r="B399" s="28">
         <v>45932</v>
       </c>
       <c r="C399" t="s">
@@ -16474,7 +16475,7 @@
       <c r="A400" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="B400" s="29">
+      <c r="B400" s="28">
         <v>45932</v>
       </c>
       <c r="C400" t="s">
@@ -16498,7 +16499,7 @@
       <c r="A401" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B401" s="29">
+      <c r="B401" s="28">
         <v>45932</v>
       </c>
       <c r="C401" t="s">
@@ -16522,7 +16523,7 @@
       <c r="A402" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B402" s="29">
+      <c r="B402" s="28">
         <v>45932</v>
       </c>
       <c r="C402" t="s">
@@ -16546,7 +16547,7 @@
       <c r="A403" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B403" s="29">
+      <c r="B403" s="28">
         <v>45932</v>
       </c>
       <c r="C403" t="s">
@@ -16570,7 +16571,7 @@
       <c r="A404" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B404" s="29">
+      <c r="B404" s="28">
         <v>45932</v>
       </c>
       <c r="C404" t="s">
@@ -16594,7 +16595,7 @@
       <c r="A405" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="B405" s="29">
+      <c r="B405" s="28">
         <v>45932</v>
       </c>
       <c r="C405" t="s">
@@ -16615,7 +16616,7 @@
       <c r="A406" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B406" s="29">
+      <c r="B406" s="28">
         <v>45932</v>
       </c>
       <c r="C406" t="s">
@@ -16639,7 +16640,7 @@
       <c r="A407" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B407" s="29">
+      <c r="B407" s="28">
         <v>45932</v>
       </c>
       <c r="C407" t="s">
@@ -16663,7 +16664,7 @@
       <c r="A408" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="B408" s="29">
+      <c r="B408" s="28">
         <v>45932</v>
       </c>
       <c r="C408" t="s">
@@ -16684,7 +16685,7 @@
       <c r="A409" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="B409" s="29">
+      <c r="B409" s="28">
         <v>45932</v>
       </c>
       <c r="C409" t="s">
@@ -16708,7 +16709,7 @@
       <c r="A410" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="B410" s="29">
+      <c r="B410" s="28">
         <v>45932</v>
       </c>
       <c r="C410" t="s">
@@ -16729,7 +16730,7 @@
       <c r="A411" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B411" s="29">
+      <c r="B411" s="28">
         <v>45932</v>
       </c>
       <c r="C411" t="s">
@@ -16750,7 +16751,7 @@
       <c r="A412" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B412" s="29">
+      <c r="B412" s="28">
         <v>45932</v>
       </c>
       <c r="C412" t="s">
@@ -16771,7 +16772,7 @@
       <c r="A413" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B413" s="29">
+      <c r="B413" s="28">
         <v>45933</v>
       </c>
       <c r="C413" t="s">
@@ -16795,7 +16796,7 @@
       <c r="A414" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B414" s="29">
+      <c r="B414" s="28">
         <v>45933</v>
       </c>
       <c r="C414" t="s">
@@ -16819,7 +16820,7 @@
       <c r="A415" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="B415" s="29">
+      <c r="B415" s="28">
         <v>45933</v>
       </c>
       <c r="C415" t="s">
@@ -16843,7 +16844,7 @@
       <c r="A416" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B416" s="29">
+      <c r="B416" s="28">
         <v>45933</v>
       </c>
       <c r="C416" t="s">
@@ -16864,7 +16865,7 @@
       <c r="A417" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B417" s="29">
+      <c r="B417" s="28">
         <v>45933</v>
       </c>
       <c r="C417" t="s">
@@ -16888,7 +16889,7 @@
       <c r="A418" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B418" s="29">
+      <c r="B418" s="28">
         <v>45933</v>
       </c>
       <c r="C418" t="s">
@@ -16912,7 +16913,7 @@
       <c r="A419" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="B419" s="29">
+      <c r="B419" s="28">
         <v>45933</v>
       </c>
       <c r="C419" t="s">
@@ -16936,7 +16937,7 @@
       <c r="A420" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="B420" s="29">
+      <c r="B420" s="28">
         <v>45933</v>
       </c>
       <c r="C420" t="s">
@@ -16960,7 +16961,7 @@
       <c r="A421" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="B421" s="29">
+      <c r="B421" s="28">
         <v>45933</v>
       </c>
       <c r="C421" t="s">
@@ -16984,7 +16985,7 @@
       <c r="A422" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B422" s="29">
+      <c r="B422" s="28">
         <v>45933</v>
       </c>
       <c r="C422" t="s">
@@ -17008,7 +17009,7 @@
       <c r="A423" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B423" s="29">
+      <c r="B423" s="28">
         <v>45933</v>
       </c>
       <c r="C423" t="s">
@@ -17032,7 +17033,7 @@
       <c r="A424" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B424" s="29">
+      <c r="B424" s="28">
         <v>45933</v>
       </c>
       <c r="C424" t="s">
@@ -17056,7 +17057,7 @@
       <c r="A425" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B425" s="29">
+      <c r="B425" s="28">
         <v>45933</v>
       </c>
       <c r="C425" t="s">
@@ -17080,7 +17081,7 @@
       <c r="A426" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="B426" s="29">
+      <c r="B426" s="28">
         <v>45933</v>
       </c>
       <c r="C426" t="s">
@@ -17101,7 +17102,7 @@
       <c r="A427" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B427" s="29">
+      <c r="B427" s="28">
         <v>45933</v>
       </c>
       <c r="C427" t="s">
@@ -17125,7 +17126,7 @@
       <c r="A428" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B428" s="29">
+      <c r="B428" s="28">
         <v>45933</v>
       </c>
       <c r="C428" t="s">
@@ -17149,7 +17150,7 @@
       <c r="A429" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="B429" s="29">
+      <c r="B429" s="28">
         <v>45933</v>
       </c>
       <c r="C429" t="s">
@@ -17170,7 +17171,7 @@
       <c r="A430" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="B430" s="29">
+      <c r="B430" s="28">
         <v>45933</v>
       </c>
       <c r="C430" t="s">
@@ -17194,7 +17195,7 @@
       <c r="A431" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="B431" s="29">
+      <c r="B431" s="28">
         <v>45933</v>
       </c>
       <c r="C431" t="s">
@@ -17215,7 +17216,7 @@
       <c r="A432" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B432" s="29">
+      <c r="B432" s="28">
         <v>45933</v>
       </c>
       <c r="C432" t="s">
@@ -17236,7 +17237,7 @@
       <c r="A433" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B433" s="29">
+      <c r="B433" s="28">
         <v>45933</v>
       </c>
       <c r="C433" t="s">
@@ -17260,7 +17261,7 @@
       <c r="A434" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B434" s="29">
+      <c r="B434" s="28">
         <v>45936</v>
       </c>
       <c r="C434" t="s">
@@ -17284,7 +17285,7 @@
       <c r="A435" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B435" s="29">
+      <c r="B435" s="28">
         <v>45936</v>
       </c>
       <c r="C435" t="s">
@@ -17308,7 +17309,7 @@
       <c r="A436" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="B436" s="29">
+      <c r="B436" s="28">
         <v>45936</v>
       </c>
       <c r="C436" t="s">
@@ -17332,7 +17333,7 @@
       <c r="A437" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B437" s="29">
+      <c r="B437" s="28">
         <v>45936</v>
       </c>
       <c r="C437" t="s">
@@ -17353,7 +17354,7 @@
       <c r="A438" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B438" s="29">
+      <c r="B438" s="28">
         <v>45936</v>
       </c>
       <c r="C438" t="s">
@@ -17377,7 +17378,7 @@
       <c r="A439" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B439" s="29">
+      <c r="B439" s="28">
         <v>45936</v>
       </c>
       <c r="C439" t="s">
@@ -17401,7 +17402,7 @@
       <c r="A440" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="B440" s="29">
+      <c r="B440" s="28">
         <v>45936</v>
       </c>
       <c r="C440" t="s">
@@ -17425,7 +17426,7 @@
       <c r="A441" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="B441" s="29">
+      <c r="B441" s="28">
         <v>45936</v>
       </c>
       <c r="C441" t="s">
@@ -17449,7 +17450,7 @@
       <c r="A442" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="B442" s="29">
+      <c r="B442" s="28">
         <v>45936</v>
       </c>
       <c r="C442" t="s">
@@ -17473,7 +17474,7 @@
       <c r="A443" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B443" s="29">
+      <c r="B443" s="28">
         <v>45936</v>
       </c>
       <c r="C443" t="s">
@@ -17497,7 +17498,7 @@
       <c r="A444" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B444" s="29">
+      <c r="B444" s="28">
         <v>45936</v>
       </c>
       <c r="C444" t="s">
@@ -17518,7 +17519,7 @@
       <c r="A445" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B445" s="29">
+      <c r="B445" s="28">
         <v>45936</v>
       </c>
       <c r="C445" t="s">
@@ -17542,7 +17543,7 @@
       <c r="A446" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B446" s="29">
+      <c r="B446" s="28">
         <v>45936</v>
       </c>
       <c r="C446" t="s">
@@ -17566,7 +17567,7 @@
       <c r="A447" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="B447" s="29">
+      <c r="B447" s="28">
         <v>45936</v>
       </c>
       <c r="C447" t="s">
@@ -17587,7 +17588,7 @@
       <c r="A448" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B448" s="29">
+      <c r="B448" s="28">
         <v>45936</v>
       </c>
       <c r="C448" t="s">
@@ -17611,7 +17612,7 @@
       <c r="A449" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B449" s="29">
+      <c r="B449" s="28">
         <v>45936</v>
       </c>
       <c r="C449" t="s">
@@ -17635,7 +17636,7 @@
       <c r="A450" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="B450" s="29">
+      <c r="B450" s="28">
         <v>45936</v>
       </c>
       <c r="C450" t="s">
@@ -17656,7 +17657,7 @@
       <c r="A451" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="B451" s="29">
+      <c r="B451" s="28">
         <v>45936</v>
       </c>
       <c r="C451" t="s">
@@ -17680,7 +17681,7 @@
       <c r="A452" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="B452" s="29">
+      <c r="B452" s="28">
         <v>45936</v>
       </c>
       <c r="C452" t="s">
@@ -17701,7 +17702,7 @@
       <c r="A453" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B453" s="29">
+      <c r="B453" s="28">
         <v>45936</v>
       </c>
       <c r="C453" t="s">
@@ -17722,7 +17723,7 @@
       <c r="A454" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B454" s="29">
+      <c r="B454" s="28">
         <v>45936</v>
       </c>
       <c r="C454" t="s">
@@ -17743,7 +17744,7 @@
       <c r="A455" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B455" s="29">
+      <c r="B455" s="28">
         <v>45937</v>
       </c>
       <c r="C455" t="s">
@@ -17767,7 +17768,7 @@
       <c r="A456" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B456" s="29">
+      <c r="B456" s="28">
         <v>45937</v>
       </c>
       <c r="C456" t="s">
@@ -17791,7 +17792,7 @@
       <c r="A457" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="B457" s="29">
+      <c r="B457" s="28">
         <v>45937</v>
       </c>
       <c r="C457" t="s">
@@ -17815,7 +17816,7 @@
       <c r="A458" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B458" s="29">
+      <c r="B458" s="28">
         <v>45937</v>
       </c>
       <c r="C458" t="s">
@@ -17836,7 +17837,7 @@
       <c r="A459" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B459" s="29">
+      <c r="B459" s="28">
         <v>45937</v>
       </c>
       <c r="C459" t="s">
@@ -17860,7 +17861,7 @@
       <c r="A460" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B460" s="29">
+      <c r="B460" s="28">
         <v>45937</v>
       </c>
       <c r="C460" t="s">
@@ -17884,7 +17885,7 @@
       <c r="A461" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="B461" s="29">
+      <c r="B461" s="28">
         <v>45937</v>
       </c>
       <c r="C461" t="s">
@@ -17908,7 +17909,7 @@
       <c r="A462" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="B462" s="29">
+      <c r="B462" s="28">
         <v>45937</v>
       </c>
       <c r="C462" t="s">
@@ -17932,7 +17933,7 @@
       <c r="A463" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="B463" s="29">
+      <c r="B463" s="28">
         <v>45937</v>
       </c>
       <c r="C463" t="s">
@@ -17953,7 +17954,7 @@
       <c r="A464" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B464" s="29">
+      <c r="B464" s="28">
         <v>45937</v>
       </c>
       <c r="C464" t="s">
@@ -17977,7 +17978,7 @@
       <c r="A465" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B465" s="29">
+      <c r="B465" s="28">
         <v>45937</v>
       </c>
       <c r="C465" t="s">
@@ -17998,7 +17999,7 @@
       <c r="A466" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B466" s="29">
+      <c r="B466" s="28">
         <v>45937</v>
       </c>
       <c r="C466" t="s">
@@ -18022,7 +18023,7 @@
       <c r="A467" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B467" s="29">
+      <c r="B467" s="28">
         <v>45937</v>
       </c>
       <c r="C467" t="s">
@@ -18046,7 +18047,7 @@
       <c r="A468" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="B468" s="29">
+      <c r="B468" s="28">
         <v>45937</v>
       </c>
       <c r="C468" t="s">
@@ -18067,7 +18068,7 @@
       <c r="A469" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B469" s="29">
+      <c r="B469" s="28">
         <v>45937</v>
       </c>
       <c r="C469" t="s">
@@ -18091,7 +18092,7 @@
       <c r="A470" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B470" s="29">
+      <c r="B470" s="28">
         <v>45937</v>
       </c>
       <c r="C470" t="s">
@@ -18115,7 +18116,7 @@
       <c r="A471" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="B471" s="29">
+      <c r="B471" s="28">
         <v>45937</v>
       </c>
       <c r="C471" t="s">
@@ -18136,7 +18137,7 @@
       <c r="A472" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="B472" s="29">
+      <c r="B472" s="28">
         <v>45937</v>
       </c>
       <c r="C472" t="s">
@@ -18160,7 +18161,7 @@
       <c r="A473" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="B473" s="29">
+      <c r="B473" s="28">
         <v>45937</v>
       </c>
       <c r="C473" t="s">
@@ -18181,7 +18182,7 @@
       <c r="A474" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B474" s="29">
+      <c r="B474" s="28">
         <v>45937</v>
       </c>
       <c r="C474" t="s">
@@ -18202,7 +18203,7 @@
       <c r="A475" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B475" s="29">
+      <c r="B475" s="28">
         <v>45937</v>
       </c>
       <c r="C475" t="s">
@@ -18226,7 +18227,7 @@
       <c r="A476" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B476" s="29">
+      <c r="B476" s="28">
         <v>45938</v>
       </c>
       <c r="C476" t="s">
@@ -18247,7 +18248,7 @@
       <c r="A477" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B477" s="29">
+      <c r="B477" s="28">
         <v>45938</v>
       </c>
       <c r="C477" t="s">
@@ -18271,7 +18272,7 @@
       <c r="A478" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="B478" s="29">
+      <c r="B478" s="28">
         <v>45938</v>
       </c>
       <c r="C478" t="s">
@@ -18295,7 +18296,7 @@
       <c r="A479" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B479" s="29">
+      <c r="B479" s="28">
         <v>45938</v>
       </c>
       <c r="C479" t="s">
@@ -18319,7 +18320,7 @@
       <c r="A480" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B480" s="29">
+      <c r="B480" s="28">
         <v>45938</v>
       </c>
       <c r="C480" t="s">
@@ -18343,7 +18344,7 @@
       <c r="A481" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B481" s="29">
+      <c r="B481" s="28">
         <v>45938</v>
       </c>
       <c r="C481" t="s">
@@ -18367,7 +18368,7 @@
       <c r="A482" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="B482" s="29">
+      <c r="B482" s="28">
         <v>45938</v>
       </c>
       <c r="C482" t="s">
@@ -18391,7 +18392,7 @@
       <c r="A483" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="B483" s="29">
+      <c r="B483" s="28">
         <v>45938</v>
       </c>
       <c r="C483" t="s">
@@ -18415,7 +18416,7 @@
       <c r="A484" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="B484" s="29">
+      <c r="B484" s="28">
         <v>45938</v>
       </c>
       <c r="C484" t="s">
@@ -18436,7 +18437,7 @@
       <c r="A485" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B485" s="29">
+      <c r="B485" s="28">
         <v>45938</v>
       </c>
       <c r="C485" t="s">
@@ -18460,7 +18461,7 @@
       <c r="A486" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B486" s="29">
+      <c r="B486" s="28">
         <v>45938</v>
       </c>
       <c r="C486" t="s">
@@ -18481,7 +18482,7 @@
       <c r="A487" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B487" s="29">
+      <c r="B487" s="28">
         <v>45938</v>
       </c>
       <c r="C487" t="s">
@@ -18502,7 +18503,7 @@
       <c r="A488" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B488" s="29">
+      <c r="B488" s="28">
         <v>45938</v>
       </c>
       <c r="C488" t="s">
@@ -18526,7 +18527,7 @@
       <c r="A489" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="B489" s="29">
+      <c r="B489" s="28">
         <v>45938</v>
       </c>
       <c r="C489" t="s">
@@ -18547,7 +18548,7 @@
       <c r="A490" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B490" s="29">
+      <c r="B490" s="28">
         <v>45938</v>
       </c>
       <c r="C490" t="s">
@@ -18571,7 +18572,7 @@
       <c r="A491" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B491" s="29">
+      <c r="B491" s="28">
         <v>45938</v>
       </c>
       <c r="C491" t="s">
@@ -18595,7 +18596,7 @@
       <c r="A492" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="B492" s="29">
+      <c r="B492" s="28">
         <v>45938</v>
       </c>
       <c r="C492" t="s">
@@ -18616,7 +18617,7 @@
       <c r="A493" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="B493" s="29">
+      <c r="B493" s="28">
         <v>45938</v>
       </c>
       <c r="C493" t="s">
@@ -18640,7 +18641,7 @@
       <c r="A494" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="B494" s="29">
+      <c r="B494" s="28">
         <v>45938</v>
       </c>
       <c r="C494" t="s">
@@ -18661,7 +18662,7 @@
       <c r="A495" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B495" s="29">
+      <c r="B495" s="28">
         <v>45938</v>
       </c>
       <c r="C495" t="s">
@@ -18682,7 +18683,7 @@
       <c r="A496" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B496" s="29">
+      <c r="B496" s="28">
         <v>45938</v>
       </c>
       <c r="C496" t="s">
@@ -18706,7 +18707,7 @@
       <c r="A497" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B497" s="29">
+      <c r="B497" s="28">
         <v>45939</v>
       </c>
       <c r="C497" t="s">
@@ -18727,7 +18728,7 @@
       <c r="A498" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B498" s="29">
+      <c r="B498" s="28">
         <v>45939</v>
       </c>
       <c r="C498" t="s">
@@ -18751,7 +18752,7 @@
       <c r="A499" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="B499" s="29">
+      <c r="B499" s="28">
         <v>45939</v>
       </c>
       <c r="C499" t="s">
@@ -18775,7 +18776,7 @@
       <c r="A500" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B500" s="29">
+      <c r="B500" s="28">
         <v>45939</v>
       </c>
       <c r="C500" t="s">
@@ -18799,7 +18800,7 @@
       <c r="A501" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B501" s="29">
+      <c r="B501" s="28">
         <v>45939</v>
       </c>
       <c r="C501" t="s">
@@ -18823,7 +18824,7 @@
       <c r="A502" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B502" s="29">
+      <c r="B502" s="28">
         <v>45939</v>
       </c>
       <c r="C502" t="s">
@@ -18847,7 +18848,7 @@
       <c r="A503" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="B503" s="29">
+      <c r="B503" s="28">
         <v>45939</v>
       </c>
       <c r="C503" t="s">
@@ -18871,7 +18872,7 @@
       <c r="A504" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="B504" s="29">
+      <c r="B504" s="28">
         <v>45939</v>
       </c>
       <c r="C504" t="s">
@@ -18895,7 +18896,7 @@
       <c r="A505" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="B505" s="29">
+      <c r="B505" s="28">
         <v>45939</v>
       </c>
       <c r="C505" t="s">
@@ -18919,7 +18920,7 @@
       <c r="A506" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B506" s="29">
+      <c r="B506" s="28">
         <v>45939</v>
       </c>
       <c r="C506" t="s">
@@ -18943,7 +18944,7 @@
       <c r="A507" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B507" s="29">
+      <c r="B507" s="28">
         <v>45939</v>
       </c>
       <c r="C507" t="s">
@@ -18967,7 +18968,7 @@
       <c r="A508" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B508" s="29">
+      <c r="B508" s="28">
         <v>45939</v>
       </c>
       <c r="C508" t="s">
@@ -18988,7 +18989,7 @@
       <c r="A509" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B509" s="29">
+      <c r="B509" s="28">
         <v>45939</v>
       </c>
       <c r="C509" t="s">
@@ -19009,7 +19010,7 @@
       <c r="A510" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="B510" s="29">
+      <c r="B510" s="28">
         <v>45939</v>
       </c>
       <c r="C510" t="s">
@@ -19030,7 +19031,7 @@
       <c r="A511" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B511" s="29">
+      <c r="B511" s="28">
         <v>45939</v>
       </c>
       <c r="C511" t="s">
@@ -19054,7 +19055,7 @@
       <c r="A512" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B512" s="29">
+      <c r="B512" s="28">
         <v>45939</v>
       </c>
       <c r="C512" t="s">
@@ -19078,7 +19079,7 @@
       <c r="A513" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="B513" s="29">
+      <c r="B513" s="28">
         <v>45939</v>
       </c>
       <c r="C513" t="s">
@@ -19099,7 +19100,7 @@
       <c r="A514" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="B514" s="29">
+      <c r="B514" s="28">
         <v>45939</v>
       </c>
       <c r="C514" t="s">
@@ -19123,7 +19124,7 @@
       <c r="A515" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="B515" s="29">
+      <c r="B515" s="28">
         <v>45939</v>
       </c>
       <c r="C515" t="s">
@@ -19144,7 +19145,7 @@
       <c r="A516" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B516" s="29">
+      <c r="B516" s="28">
         <v>45939</v>
       </c>
       <c r="C516" t="s">
@@ -19165,7 +19166,7 @@
       <c r="A517" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B517" s="29">
+      <c r="B517" s="28">
         <v>45939</v>
       </c>
       <c r="C517" t="s">
@@ -56130,13 +56131,3094 @@
       <c r="F2093" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="G2093" s="26" t="s">
+      <c r="G2093" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2094" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2094" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2094" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C2094" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2094" s="27" t="str">
+        <f>TEXT(B2094, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E2094">
+        <v>6459</v>
+      </c>
+      <c r="F2094" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2094" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2095" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2095" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2095" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C2095" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2095" s="27" t="str">
+        <f>TEXT(B2095, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E2095">
+        <v>10443</v>
+      </c>
+      <c r="F2095" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2095" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2096" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2096" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2096" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C2096" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2096" s="27" t="str">
+        <f>TEXT(B2096, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E2096">
+        <v>3994</v>
+      </c>
+      <c r="F2096" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2096" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2097" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2097" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2097" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C2097" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2097" s="27" t="str">
+        <f>TEXT(B2097, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E2097">
+        <v>72</v>
+      </c>
+      <c r="F2097" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2097" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2098" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2098" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2098" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C2098" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2098" s="27" t="str">
+        <f>TEXT(B2099, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E2098">
+        <v>3278.4</v>
+      </c>
+      <c r="F2098" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2098" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2099" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2099" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2099" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C2099" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2099" s="27" t="str">
+        <f>TEXT(B2100, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E2099">
+        <v>3240</v>
+      </c>
+      <c r="F2099" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2099" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2100" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2100" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C2100" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2100" s="27" t="str">
+        <f>TEXT(B2100, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E2100">
+        <v>5028</v>
+      </c>
+      <c r="F2100" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2100" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2101" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2101" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C2101" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2101" s="27" t="str">
+        <f>TEXT(B2101, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E2101">
+        <v>7976.8</v>
+      </c>
+      <c r="F2101" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2101" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2102" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2102" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C2102" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2102" s="27" t="str">
+        <f>TEXT(B2102, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E2102">
+        <v>7164</v>
+      </c>
+      <c r="F2102" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2102" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2103" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2103" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C2103" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2103" s="27" t="str">
+        <f>TEXT(B2103, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E2103">
+        <v>3072</v>
+      </c>
+      <c r="F2103" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2103" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2104" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2104" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C2104" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2104" s="27" t="str">
+        <f>TEXT(B2104, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="F2104" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2104" s="27" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2105" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2105" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C2105" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2105" s="27" t="str">
+        <f>TEXT(B2105, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E2105">
+        <v>6416</v>
+      </c>
+      <c r="F2105" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2105" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2106" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2106" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C2106" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2106" s="27" t="str">
+        <f>TEXT(B2106, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="F2106" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2106" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2107" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2107" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C2107" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2107" s="27" t="str">
+        <f>TEXT(B2107, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E2107">
+        <v>8267</v>
+      </c>
+      <c r="F2107" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2107" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2108" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2108" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C2108" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2108" s="27" t="str">
+        <f>TEXT(B2108, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E2108">
+        <v>13211</v>
+      </c>
+      <c r="F2108" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2108" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2109" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2109" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C2109" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2109" s="27" t="str">
+        <f>TEXT(B2109, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E2109">
+        <v>19484</v>
+      </c>
+      <c r="F2109" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2109" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2110" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2110" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C2110" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2110" s="27" t="str">
+        <f>TEXT(B2110, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E2110">
+        <v>1617</v>
+      </c>
+      <c r="F2110" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2110" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2111" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2111" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C2111" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2111" s="27" t="str">
+        <f>TEXT(B2111, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E2111">
+        <v>751</v>
+      </c>
+      <c r="F2111" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2111" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2112" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2112" s="2">
+        <v>46114</v>
+      </c>
+      <c r="C2112" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2112" s="27" t="str">
+        <f>TEXT(B2112, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E2112">
+        <v>6153</v>
+      </c>
+      <c r="F2112" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2112" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2113" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2113" s="2">
+        <v>46114</v>
+      </c>
+      <c r="C2113" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2113" s="27" t="str">
+        <f>TEXT(B2113, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E2113">
+        <v>1432</v>
+      </c>
+      <c r="F2113" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2113" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2114" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2114" s="2">
+        <v>46114</v>
+      </c>
+      <c r="C2114" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2114" s="27" t="str">
+        <f>TEXT(B2114, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="F2114" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2114" s="27" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2115" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2115" s="2">
+        <v>46114</v>
+      </c>
+      <c r="C2115" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2115" s="27" t="str">
+        <f>TEXT(B2115, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="F2115" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2115" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2116" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2116" s="2">
+        <v>46114</v>
+      </c>
+      <c r="C2116" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2116" s="27" t="str">
+        <f>TEXT(B2117, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E2116">
+        <v>1963.8</v>
+      </c>
+      <c r="F2116" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2116" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2117" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2117" s="2">
+        <v>46114</v>
+      </c>
+      <c r="C2117" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2117" s="27" t="str">
+        <f>TEXT(B2118, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E2117">
+        <v>4222.8</v>
+      </c>
+      <c r="F2117" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2117" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2118" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2118" s="2">
+        <v>46114</v>
+      </c>
+      <c r="C2118" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2118" s="27" t="str">
+        <f>TEXT(B2118, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E2118">
+        <v>2468</v>
+      </c>
+      <c r="F2118" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2118" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2119" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2119" s="2">
+        <v>46114</v>
+      </c>
+      <c r="C2119" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2119" s="27" t="str">
+        <f>TEXT(B2119, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E2119">
+        <v>4972.6000000000004</v>
+      </c>
+      <c r="F2119" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2119" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2120" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2120" s="2">
+        <v>46114</v>
+      </c>
+      <c r="C2120" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2120" s="27" t="str">
+        <f>TEXT(B2120, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="F2120" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2120" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2121" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2121" s="2">
+        <v>46114</v>
+      </c>
+      <c r="C2121" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2121" s="27" t="str">
+        <f>TEXT(B2121, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E2121">
+        <v>7916</v>
+      </c>
+      <c r="F2121" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2121" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2122" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2122" s="2">
+        <v>46114</v>
+      </c>
+      <c r="C2122" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2122" s="27" t="str">
+        <f>TEXT(B2122, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E2122">
+        <v>10660.4</v>
+      </c>
+      <c r="F2122" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2122" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2123" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2123" s="2">
+        <v>46114</v>
+      </c>
+      <c r="C2123" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2123" s="27" t="str">
+        <f>TEXT(B2123, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E2123">
+        <v>11188</v>
+      </c>
+      <c r="F2123" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2123" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2124" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2124" s="2">
+        <v>46114</v>
+      </c>
+      <c r="C2124" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2124" s="27" t="str">
+        <f>TEXT(B2124, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E2124">
+        <v>12212</v>
+      </c>
+      <c r="F2124" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2124" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2125" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2125" s="2">
+        <v>46114</v>
+      </c>
+      <c r="C2125" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2125" s="27" t="str">
+        <f>TEXT(B2125, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E2125">
+        <v>9176</v>
+      </c>
+      <c r="F2125" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2125" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2126" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2126" s="2">
+        <v>46114</v>
+      </c>
+      <c r="C2126" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2126" s="27" t="str">
+        <f>TEXT(B2126, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E2126">
+        <v>1843</v>
+      </c>
+      <c r="F2126" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2126" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2127" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2127" s="2">
+        <v>46114</v>
+      </c>
+      <c r="C2127" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2127" s="27" t="str">
+        <f>TEXT(B2127, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E2127">
+        <v>689</v>
+      </c>
+      <c r="F2127" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2127" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2128" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2128" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C2128" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2128" s="27" t="str">
+        <f>TEXT(B2128, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="E2128">
+        <v>2483</v>
+      </c>
+      <c r="F2128" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2128" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2129" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2129" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C2129" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2129" s="27" t="str">
+        <f>TEXT(B2129, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="E2129">
+        <v>1711</v>
+      </c>
+      <c r="F2129" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2129" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2130" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2130" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C2130" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2130" s="27" t="str">
+        <f>TEXT(B2130, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="E2130">
+        <v>2472</v>
+      </c>
+      <c r="F2130" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2130" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2131" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2131" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C2131" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2131" s="27" t="str">
+        <f>TEXT(B2131, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="F2131" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2131" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2132" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2132" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C2132" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2132" s="27" t="str">
+        <f>TEXT(B2133, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="E2132">
+        <v>2390.4</v>
+      </c>
+      <c r="F2132" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2132" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2133" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2133" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C2133" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2133" s="27" t="str">
+        <f>TEXT(B2134, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="E2133">
+        <v>2127</v>
+      </c>
+      <c r="F2133" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2133" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2134" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2134" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C2134" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2134" s="27" t="str">
+        <f>TEXT(B2134, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="E2134">
+        <v>1492</v>
+      </c>
+      <c r="F2134" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2134" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2135" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2135" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C2135" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2135" s="27" t="str">
+        <f>TEXT(B2135, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="E2135">
+        <v>4615.2</v>
+      </c>
+      <c r="F2135" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2135" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2136" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2136" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C2136" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2136" s="27" t="str">
+        <f>TEXT(B2136, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="F2136" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2136" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2137" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2137" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C2137" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2137" s="27" t="str">
+        <f>TEXT(B2137, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="E2137">
+        <v>1068</v>
+      </c>
+      <c r="F2137" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2137" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2138" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2138" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C2138" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2138" s="27" t="str">
+        <f>TEXT(B2138, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="E2138">
+        <v>4764.8999999999996</v>
+      </c>
+      <c r="F2138" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2138" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2139" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2139" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C2139" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2139" s="27" t="str">
+        <f>TEXT(B2139, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="F2139" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2139" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2140" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2140" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C2140" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2140" s="27" t="str">
+        <f>TEXT(B2140, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="E2140">
+        <v>7035</v>
+      </c>
+      <c r="F2140" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2140" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2141" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2141" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C2141" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2141" s="27" t="str">
+        <f>TEXT(B2141, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="E2141">
+        <v>3303</v>
+      </c>
+      <c r="F2141" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2141" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2142" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2142" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C2142" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2142" s="27" t="str">
+        <f>TEXT(B2142, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="F2142" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2142" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2143" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2143" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C2143" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2143" s="27" t="str">
+        <f>TEXT(B2143, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="E2143">
+        <v>648</v>
+      </c>
+      <c r="F2143" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2143" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2144" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2144" s="2">
+        <v>46118</v>
+      </c>
+      <c r="C2144" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2144" s="27" t="str">
+        <f>TEXT(B2144, "dddd")</f>
+        <v>Monday</v>
+      </c>
+      <c r="E2144">
+        <v>3668</v>
+      </c>
+      <c r="F2144" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2144" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2145" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2145" s="2">
+        <v>46118</v>
+      </c>
+      <c r="C2145" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2145" s="27" t="str">
+        <f>TEXT(B2145, "dddd")</f>
+        <v>Monday</v>
+      </c>
+      <c r="E2145">
+        <v>3329</v>
+      </c>
+      <c r="F2145" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2145" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2146" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2146" s="2">
+        <v>46118</v>
+      </c>
+      <c r="C2146" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2146" s="27" t="str">
+        <f>TEXT(B2146, "dddd")</f>
+        <v>Monday</v>
+      </c>
+      <c r="E2146">
+        <v>3027</v>
+      </c>
+      <c r="F2146" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2146" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2147" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2147" s="2">
+        <v>46118</v>
+      </c>
+      <c r="C2147" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2147" s="27" t="str">
+        <f>TEXT(B2147, "dddd")</f>
+        <v>Monday</v>
+      </c>
+      <c r="E2147">
+        <v>28.8</v>
+      </c>
+      <c r="F2147" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2147" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2148" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2148" s="2">
+        <v>46118</v>
+      </c>
+      <c r="C2148" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2148" s="27" t="str">
+        <f>TEXT(B2149, "dddd")</f>
+        <v>Monday</v>
+      </c>
+      <c r="F2148" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2148" s="27" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2149" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2149" s="2">
+        <v>46118</v>
+      </c>
+      <c r="C2149" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2149" s="27" t="str">
+        <f>TEXT(B2150, "dddd")</f>
+        <v>Monday</v>
+      </c>
+      <c r="E2149">
+        <v>2957.7</v>
+      </c>
+      <c r="F2149" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2149" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2150" spans="1:7" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2150" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2150" s="2">
+        <v>46118</v>
+      </c>
+      <c r="C2150" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2150" s="27" t="str">
+        <f>TEXT(B2150, "dddd")</f>
+        <v>Monday</v>
+      </c>
+      <c r="E2150">
+        <v>319.2</v>
+      </c>
+      <c r="F2150" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2150" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2151" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2151" s="2">
+        <v>46118</v>
+      </c>
+      <c r="C2151" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2151" s="27" t="str">
+        <f>TEXT(B2151, "dddd")</f>
+        <v>Monday</v>
+      </c>
+      <c r="E2151">
+        <v>10768.8</v>
+      </c>
+      <c r="F2151" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2151" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2152" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2152" s="2">
+        <v>46118</v>
+      </c>
+      <c r="C2152" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2152" s="27" t="str">
+        <f>TEXT(B2152, "dddd")</f>
+        <v>Monday</v>
+      </c>
+      <c r="F2152" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2152" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2153" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2153" s="2">
+        <v>46118</v>
+      </c>
+      <c r="C2153" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2153" s="27" t="str">
+        <f>TEXT(B2153, "dddd")</f>
+        <v>Monday</v>
+      </c>
+      <c r="F2153" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2153" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2154" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2154" s="2">
+        <v>46118</v>
+      </c>
+      <c r="C2154" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2154" s="27" t="str">
+        <f>TEXT(B2154, "dddd")</f>
+        <v>Monday</v>
+      </c>
+      <c r="E2154">
+        <v>5955</v>
+      </c>
+      <c r="F2154" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2154" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2155" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2155" s="2">
+        <v>46118</v>
+      </c>
+      <c r="C2155" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2155" s="27" t="str">
+        <f>TEXT(B2155, "dddd")</f>
+        <v>Monday</v>
+      </c>
+      <c r="E2155">
+        <v>5562</v>
+      </c>
+      <c r="F2155" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2155" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2156" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2156" s="2">
+        <v>46118</v>
+      </c>
+      <c r="C2156" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2156" s="27" t="str">
+        <f>TEXT(B2156, "dddd")</f>
+        <v>Monday</v>
+      </c>
+      <c r="E2156">
+        <v>15622</v>
+      </c>
+      <c r="F2156" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2156" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2157" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2157" s="2">
+        <v>46118</v>
+      </c>
+      <c r="C2157" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2157" s="27" t="str">
+        <f>TEXT(B2157, "dddd")</f>
+        <v>Monday</v>
+      </c>
+      <c r="E2157">
+        <v>3930</v>
+      </c>
+      <c r="F2157" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2157" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2158" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2158" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2158" s="2">
+        <v>46118</v>
+      </c>
+      <c r="C2158" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2158" s="27" t="str">
+        <f>TEXT(B2158, "dddd")</f>
+        <v>Monday</v>
+      </c>
+      <c r="E2158">
+        <v>2280</v>
+      </c>
+      <c r="F2158" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2158" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2159" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2159" s="2">
+        <v>46118</v>
+      </c>
+      <c r="C2159" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2159" s="27" t="str">
+        <f>TEXT(B2159, "dddd")</f>
+        <v>Monday</v>
+      </c>
+      <c r="E2159">
+        <v>1900</v>
+      </c>
+      <c r="F2159" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2159" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2160" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2160" s="2">
+        <v>46119</v>
+      </c>
+      <c r="C2160" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2160" s="27" t="str">
+        <f>TEXT(B2160, "dddd")</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="E2160">
+        <v>5279</v>
+      </c>
+      <c r="F2160" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2160" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2161" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2161" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2161" s="2">
+        <v>46119</v>
+      </c>
+      <c r="C2161" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2161" s="27" t="str">
+        <f>TEXT(B2161, "dddd")</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="E2161">
+        <v>4320</v>
+      </c>
+      <c r="F2161" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2161" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2162" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2162" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2162" s="2">
+        <v>46119</v>
+      </c>
+      <c r="C2162" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2162" s="27" t="str">
+        <f>TEXT(B2162, "dddd")</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="E2162">
+        <v>8297</v>
+      </c>
+      <c r="F2162" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2162" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2163" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2163" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2163" s="2">
+        <v>46119</v>
+      </c>
+      <c r="C2163" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2163" s="27" t="str">
+        <f>TEXT(B2163, "dddd")</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="E2163">
+        <v>150</v>
+      </c>
+      <c r="F2163" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2163" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2164" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2164" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2164" s="2">
+        <v>46119</v>
+      </c>
+      <c r="C2164" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2164" s="27" t="str">
+        <f>TEXT(B2165, "dddd")</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="E2164">
+        <v>531.29999999999995</v>
+      </c>
+      <c r="F2164" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2164" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2165" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2165" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2165" s="2">
+        <v>46119</v>
+      </c>
+      <c r="C2165" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2165" s="27" t="str">
+        <f>TEXT(B2166, "dddd")</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="E2165">
+        <v>2369.3000000000002</v>
+      </c>
+      <c r="F2165" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2165" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2166" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2166" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2166" s="2">
+        <v>46119</v>
+      </c>
+      <c r="C2166" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2166" s="27" t="str">
+        <f>TEXT(B2166, "dddd")</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="F2166" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2166" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2167" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2167" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2167" s="2">
+        <v>46119</v>
+      </c>
+      <c r="C2167" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2167" s="27" t="str">
+        <f>TEXT(B2167, "dddd")</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="E2167">
+        <v>10766</v>
+      </c>
+      <c r="F2167" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2167" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2168" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2168" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2168" s="2">
+        <v>46119</v>
+      </c>
+      <c r="C2168" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2168" s="27" t="str">
+        <f>TEXT(B2168, "dddd")</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="E2168">
+        <v>4615.2</v>
+      </c>
+      <c r="F2168" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2168" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2169" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2169" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2169" s="2">
+        <v>46119</v>
+      </c>
+      <c r="C2169" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2169" s="27" t="str">
+        <f>TEXT(B2169, "dddd")</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="F2169" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2169" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2170" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2170" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2170" s="2">
+        <v>46119</v>
+      </c>
+      <c r="C2170" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2170" s="27" t="str">
+        <f>TEXT(B2170, "dddd")</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="F2170" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2170" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2171" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2171" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2171" s="2">
+        <v>46119</v>
+      </c>
+      <c r="C2171" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2171" s="27" t="str">
+        <f>TEXT(B2171, "dddd")</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="E2171">
+        <v>1875.8</v>
+      </c>
+      <c r="F2171" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2171" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2172" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2172" s="2">
+        <v>46119</v>
+      </c>
+      <c r="C2172" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2172" s="27" t="str">
+        <f>TEXT(B2172, "dddd")</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="E2172">
+        <v>7642</v>
+      </c>
+      <c r="F2172" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2172" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2173" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2173" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2173" s="2">
+        <v>46119</v>
+      </c>
+      <c r="C2173" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2173" s="27" t="str">
+        <f>TEXT(B2173, "dddd")</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="E2173">
+        <v>17027</v>
+      </c>
+      <c r="F2173" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2173" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2174" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2174" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2174" s="2">
+        <v>46119</v>
+      </c>
+      <c r="C2174" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2174" s="27" t="str">
+        <f>TEXT(B2174, "dddd")</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="E2174">
+        <v>9281</v>
+      </c>
+      <c r="F2174" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2174" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2175" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2175" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2175" s="2">
+        <v>46119</v>
+      </c>
+      <c r="C2175" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2175" s="27" t="str">
+        <f>TEXT(B2175, "dddd")</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="E2175">
+        <v>2565</v>
+      </c>
+      <c r="F2175" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2175" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2176" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2176" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2176" s="2">
+        <v>46119</v>
+      </c>
+      <c r="C2176" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2176" s="27" t="str">
+        <f>TEXT(B2176, "dddd")</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="E2176">
+        <v>2044</v>
+      </c>
+      <c r="F2176" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2176" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2177" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2177" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2177" s="2">
+        <v>46120</v>
+      </c>
+      <c r="C2177" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2177" s="27" t="str">
+        <f>TEXT(B2177, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E2177">
+        <v>3014.6</v>
+      </c>
+      <c r="F2177" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2177" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2178" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2178" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2178" s="2">
+        <v>46120</v>
+      </c>
+      <c r="C2178" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2178" s="27" t="str">
+        <f>TEXT(B2178, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E2178">
+        <v>3530</v>
+      </c>
+      <c r="F2178" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2178" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2179" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2179" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2179" s="2">
+        <v>46120</v>
+      </c>
+      <c r="C2179" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2179" s="27" t="str">
+        <f>TEXT(B2179, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E2179">
+        <v>7600</v>
+      </c>
+      <c r="F2179" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2179" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2180" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2180" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2180" s="2">
+        <v>46120</v>
+      </c>
+      <c r="C2180" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2180" s="27" t="str">
+        <f>TEXT(B2180, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E2180">
+        <v>199.6</v>
+      </c>
+      <c r="F2180" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2180" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2181" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2181" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2181" s="2">
+        <v>46120</v>
+      </c>
+      <c r="C2181" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2181" s="27" t="str">
+        <f>TEXT(B2182, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E2181">
+        <v>2177</v>
+      </c>
+      <c r="F2181" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2181" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2182" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2182" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2182" s="2">
+        <v>46120</v>
+      </c>
+      <c r="C2182" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2182" s="27" t="str">
+        <f>TEXT(B2183, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E2182">
+        <v>2290.8000000000002</v>
+      </c>
+      <c r="F2182" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2182" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2183" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2183" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2183" s="2">
+        <v>46120</v>
+      </c>
+      <c r="C2183" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2183" s="27" t="str">
+        <f>TEXT(B2183, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E2183">
+        <v>3240</v>
+      </c>
+      <c r="F2183" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2183" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2184" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2184" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2184" s="2">
+        <v>46120</v>
+      </c>
+      <c r="C2184" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2184" s="27" t="str">
+        <f>TEXT(B2184, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E2184">
+        <v>2520</v>
+      </c>
+      <c r="F2184" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2184" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2185" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2185" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2185" s="2">
+        <v>46120</v>
+      </c>
+      <c r="C2185" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2185" s="27" t="str">
+        <f>TEXT(B2185, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="F2185" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2185" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2186" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2186" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2186" s="2">
+        <v>46120</v>
+      </c>
+      <c r="C2186" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2186" s="27" t="str">
+        <f>TEXT(B2186, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E2186">
+        <v>6644</v>
+      </c>
+      <c r="F2186" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2186" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2187" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2187" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2187" s="2">
+        <v>46120</v>
+      </c>
+      <c r="C2187" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2187" s="27" t="str">
+        <f>TEXT(B2187, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E2187">
+        <v>10017.9</v>
+      </c>
+      <c r="F2187" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2187" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2188" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2188" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2188" s="2">
+        <v>46120</v>
+      </c>
+      <c r="C2188" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2188" s="27" t="str">
+        <f>TEXT(B2188, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E2188">
+        <v>12387</v>
+      </c>
+      <c r="F2188" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2188" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2189" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2189" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2189" s="2">
+        <v>46120</v>
+      </c>
+      <c r="C2189" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2189" s="27" t="str">
+        <f>TEXT(B2189, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E2189">
+        <v>15309</v>
+      </c>
+      <c r="F2189" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2189" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2190" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2190" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2190" s="2">
+        <v>46120</v>
+      </c>
+      <c r="C2190" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2190" s="27" t="str">
+        <f>TEXT(B2190, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E2190" s="27">
+        <v>9421</v>
+      </c>
+      <c r="F2190" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2190" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2191" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2191" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2191" s="2">
+        <v>46120</v>
+      </c>
+      <c r="C2191" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2191" s="27" t="str">
+        <f>TEXT(B2191, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E2191">
+        <v>1986</v>
+      </c>
+      <c r="F2191" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2191" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2192" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2192" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2192" s="2">
+        <v>46120</v>
+      </c>
+      <c r="C2192" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2192" s="27" t="str">
+        <f>TEXT(B2192, "dddd")</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="E2192">
+        <v>1663</v>
+      </c>
+      <c r="F2192" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2192" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2193" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2193" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2193" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C2193" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2193" s="27" t="str">
+        <f>TEXT(B2193, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E2193">
+        <v>2044.2</v>
+      </c>
+      <c r="F2193" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2193" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2194" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2194" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2194" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C2194" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2194" s="27" t="str">
+        <f>TEXT(B2194, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E2194">
+        <v>4989</v>
+      </c>
+      <c r="F2194" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2194" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2195" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2195" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2195" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C2195" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2195" s="27" t="str">
+        <f>TEXT(B2195, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E2195">
+        <v>6854</v>
+      </c>
+      <c r="F2195" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2195" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2196" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2196" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2196" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C2196" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2196" s="27" t="str">
+        <f>TEXT(B2196, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E2196">
+        <v>204</v>
+      </c>
+      <c r="F2196" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2196" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2197" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2197" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2197" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C2197" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2197" s="27" t="str">
+        <f>TEXT(B2198, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="F2197" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2197" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2198" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2198" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2198" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C2198" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2198" s="27" t="str">
+        <f>TEXT(B2199, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E2198">
+        <v>3537.2</v>
+      </c>
+      <c r="F2198" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2198" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2199" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2199" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2199" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C2199" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2199" s="27" t="str">
+        <f>TEXT(B2199, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E2199">
+        <v>1374</v>
+      </c>
+      <c r="F2199" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2199" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2200" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2200" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2200" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C2200" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2200" s="27" t="str">
+        <f>TEXT(B2200, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E2200">
+        <v>10080</v>
+      </c>
+      <c r="F2200" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2200" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2201" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2201" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2201" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C2201" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2201" s="27" t="str">
+        <f>TEXT(B2201, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="F2201" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2201" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2202" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2202" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2202" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C2202" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2202" s="27" t="str">
+        <f>TEXT(B2202, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E2202">
+        <v>7940</v>
+      </c>
+      <c r="F2202" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2202" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2203" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2203" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2203" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C2203" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2203" s="27" t="str">
+        <f>TEXT(B2203, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E2203">
+        <v>4673.3999999999996</v>
+      </c>
+      <c r="F2203" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2203" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2204" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2204" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2204" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C2204" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2204" s="27" t="str">
+        <f>TEXT(B2204, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E2204">
+        <v>13180</v>
+      </c>
+      <c r="F2204" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2204" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2205" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2205" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2205" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C2205" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2205" s="27" t="str">
+        <f>TEXT(B2205, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E2205">
+        <v>16538</v>
+      </c>
+      <c r="F2205" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2205" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2206" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2206" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2206" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C2206" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2206" s="27" t="str">
+        <f>TEXT(B2206, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E2206">
+        <v>8808</v>
+      </c>
+      <c r="F2206" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2206" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2207" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2207" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2207" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C2207" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2207" s="27" t="str">
+        <f>TEXT(B2207, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="F2207" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2207" s="27" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2208" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2208" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2208" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C2208" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2208" s="27" t="str">
+        <f>TEXT(B2208, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="E2208">
+        <v>768</v>
+      </c>
+      <c r="F2208" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2208" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2209" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2209" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2209" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C2209" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2209" s="27" t="str">
+        <f>TEXT(B2209, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="E2209">
+        <v>5163.2</v>
+      </c>
+      <c r="F2209" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2209" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2210" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2210" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2210" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C2210" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2210" s="27" t="str">
+        <f>TEXT(B2210, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="E2210">
+        <v>3045</v>
+      </c>
+      <c r="F2210" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2210" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2211" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2211" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2211" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C2211" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2211" s="27" t="str">
+        <f>TEXT(B2211, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="E2211">
+        <v>6320</v>
+      </c>
+      <c r="F2211" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2211" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2212" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2212" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2212" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C2212" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2212" s="27" t="str">
+        <f>TEXT(B2212, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="E2212">
+        <v>180</v>
+      </c>
+      <c r="F2212" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2212" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2213" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2213" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2213" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C2213" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2213" s="27" t="str">
+        <f>TEXT(B2214, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="E2213">
+        <v>2040.4</v>
+      </c>
+      <c r="F2213" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2213" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2214" spans="1:7" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2214" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2214" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C2214" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2214" s="27" t="str">
+        <f>TEXT(B2215, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="E2214">
+        <v>2402.1999999999998</v>
+      </c>
+      <c r="F2214" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2214" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2215" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2215" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2215" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C2215" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2215" s="27" t="str">
+        <f>TEXT(B2215, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="E2215">
+        <v>2713</v>
+      </c>
+      <c r="F2215" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2215" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2216" spans="1:7" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2216" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2216" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C2216" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2216" s="27" t="str">
+        <f>TEXT(B2216, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="E2216" s="27">
+        <v>5749.2</v>
+      </c>
+      <c r="F2216" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2216" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2217" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2217" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2217" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C2217" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2217" s="27" t="str">
+        <f>TEXT(B2217, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="F2217" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2217" s="27" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2218" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2218" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2218" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C2218" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2218" s="27" t="str">
+        <f>TEXT(B2218, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="F2218" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2218" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2219" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2219" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2219" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C2219" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2219" s="27" t="str">
+        <f>TEXT(B2219, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="E2219">
+        <v>8825.5</v>
+      </c>
+      <c r="F2219" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2219" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2220" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2220" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2220" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C2220" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2220" s="27" t="str">
+        <f>TEXT(B2220, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="E2220">
+        <v>11424</v>
+      </c>
+      <c r="F2220" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2220" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2221" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2221" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2221" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C2221" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2221" s="27" t="str">
+        <f>TEXT(B2221, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="E2221">
+        <v>16225</v>
+      </c>
+      <c r="F2221" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2221" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2222" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2222" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2222" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C2222" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2222" s="27" t="str">
+        <f>TEXT(B2222, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="E2222">
+        <v>12519</v>
+      </c>
+      <c r="F2222" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2222" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2223" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2223" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2223" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C2223" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2223" s="27" t="str">
+        <f>TEXT(B2223, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="E2223">
+        <v>1757</v>
+      </c>
+      <c r="F2223" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2223" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2224" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2224" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2224" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C2224" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2224" s="27" t="str">
+        <f>TEXT(B2224, "dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="E2224">
+        <v>2977</v>
+      </c>
+      <c r="F2224" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2224" s="27" t="s">
         <v>39</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G1372" xr:uid="{00000000-0001-0000-0200-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G2093">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G2224">
       <sortCondition ref="B1:B1372"/>
     </sortState>
   </autoFilter>
